--- a/data/env_test/case_excle/Productization_trade/case_data.xlsx
+++ b/data/env_test/case_excle/Productization_trade/case_data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/Downloads/zhongshu---qingyuan-ce6ef9d61be80ed5c3abf49706731e1822c5c44c 2/data/env_test/case_excle/sd/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\InterfaceAutomaticTesttPlatform\data\env_test\case_excle\Productization_trade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C77C81-7926-2E49-ADB2-BC1ADC72E1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7588219A-ED88-4FBB-9995-4E1B6B9F3C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1-招标-excle" sheetId="10" r:id="rId1"/>
+    <sheet name="公开" sheetId="10" r:id="rId1"/>
     <sheet name="1-投标-excle" sheetId="11" r:id="rId2"/>
     <sheet name="2-投标-excle" sheetId="12" r:id="rId3"/>
     <sheet name="3-投标-excle" sheetId="7" r:id="rId4"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="481">
   <si>
     <t>编号</t>
   </si>
@@ -177,19 +177,7 @@
     <t>a12</t>
   </si>
   <si>
-    <t>文件预上传</t>
-  </si>
-  <si>
     <t>brace/file/upload/resume/chunk</t>
-  </si>
-  <si>
-    <t>{"fileId":"$.data.id"}</t>
-  </si>
-  <si>
-    <t>a13</t>
-  </si>
-  <si>
-    <t>文件上传</t>
   </si>
   <si>
     <t>a14</t>
@@ -1219,540 +1207,374 @@
   </si>
   <si>
     <t>etbuser/ztkLogin</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tpPurchaseNeed?submit=true</t>
-  </si>
-  <si>
-    <t>审批</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>创建需求</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>查询需求</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>创建采购计划</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tpPurchasePlan?submit=true</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>查询采购计划</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"comment":"","taskLocalVariables":{"approveFiles":""},"businessKey":"${needId}","processVariables":{}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"planId": "$.data.list[0].id"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"comment":"","taskLocalVariables":{"approveFiles":""},"businessKey":"${planId}","processVariables":{}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","needContent":"","needMaterialList":[{"brand":"1821742140835680258","brandName":"小米","classifyCode":"HW009002001","classifyId":"1821737321655881730","classifyName":"连花清瘟","customIndex":"0","materialCode":"HW009002001001","materialCount":"1000","materialId":"1821742325708017666","materialName":"小米连花清瘟","measureUnit":"盒","price":"120","skuId":"1821742672992194561","skuParam":"","specification":"5","specificationId":"1821742672992194561","totalPrice":"120000","unit":"盒"},{"brand":"1821742140835680258","brandName":"小米","classifyCode":"HW009002001","classifyId":"1821737321655881730","classifyName":"连花清瘟","customIndex":"1","materialCode":"HW009002001001","materialCount":"1000","materialId":"1821742325708017666","materialName":"小米连花清瘟","measureUnit":"盒","price":"210","skuId":"1821742716164165634","skuParam":"","specification":"10","specificationId":"1821742716164165634","totalPrice":"210000","unit":"盒"},{"brand":"1821742140835680258","brandName":"小米","classifyCode":"HW009002001","classifyId":"1821737321655881730","classifyName":"连花清瘟","customIndex":"2","materialCode":"HW009002001001","materialCount":"1000","materialId":"1821742325708017666","materialName":"小米连花清瘟","measureUnit":"盒","price":"400","skuId":"1821742751215964161","skuParam":"","specification":"20","specificationId":"1821742751215964161","totalPrice":"400000","unit":"盒"},{"brand":"1821742140835680258","brandName":"小米","classifyCode":"HW009002004","classifyId":"1844932356959940610","classifyName":"感冒灵","customIndex":"3","materialCode":"HW009002004001","materialCount":"1000","materialId":"1844934129661554689","materialName":"999感冒灵","measureUnit":"箱","price":"1200","skuId":"1844934395131637761","skuParam":"","specification":"GB20241012-0001","specificationId":"1844934395131637761","totalPrice":"1200000","unit":"箱"},{"brand":"1821742140835680258","brandName":"小米","classifyCode":"HW009002004","classifyId":"1844932356959940610","classifyName":"感冒灵","customIndex":"4","materialCode":"HW009002004001","materialCount":"1000","materialId":"1844934129661554689","materialName":"999感冒灵","measureUnit":"箱","price":"1000","skuId":"1844934521673789442","skuParam":"","specification":"GB20240912-001","specificationId":"1844934521673789442","totalPrice":"1000000","unit":"箱"}],"needType":"1821737321655881730,1821737383786106882,1821737427427840001,1844932356959940610","needTypeList":[],"purchaseCatalog":"HW","purchaseNeedName":"${purchaseProjectName}","userId":"1815283718319951872","userName":"集采中心负责人"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tpPurchaseNeed/page?taskStatus=1&amp;current=1&amp;size=10&amp;total=249&amp;purchaseNeedName=${purchaseProjectNameDecode}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tpPurchasePlan/page?taskStatus=1&amp;planName=${purchaseProjectNameDecode}&amp;current=1&amp;size=10&amp;total=294</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"needId":"$.data.list[0].id"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>查询需求详情</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tpPurchaseNeed/${needId}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"needMaterialId1":"$.data.needMaterialList[3].id","needMaterialId2":"$.data.needMaterialList[4].id"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"totalPrice":"2200000","bigTotalPrice":"贰佰贰拾万元整","remark":"","fileIds":"","needMaterialList":[],"purchaseType":"6","planName":"${purchaseProjectName}","linkman":"测试","materialType":"HW","proType":"2","linkmanTel":"13909090807","infoMaterialList":[{"tpPurchaseNeedId":"${needId}","classifyName":"感冒灵","classifyCode":"HW009002004","classifyId":"1844932356959940610","materialId":"1844934129661554689","materialName":"999感冒灵","materialCount":"1000","unit":"箱","planUseTime":"","price":"1000","priceCn":"","totalPrice":"1000000","totalPriceCn":"","remark":"","leftCount":"","status":"0","purchaseType":"","specification":"GB20240912-001","specificationId":"1844934521673789442","materialCode":"HW009002004001","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","brand":"1821742140835680258","brandName":"小米","insertTime":"2024-12-05 11:31:44","insertPersonName":"集采中心负责人","tpPurchaseNeedMaterialId":"${needMaterialId1}","customIndex":"0"},{"tpPurchaseNeedId":"${needId}","classifyName":"感冒灵","classifyCode":"HW009002004","classifyId":"1844932356959940610","materialId":"1844934129661554689","materialName":"999感冒灵","materialCount":"1000","unit":"箱","planUseTime":"","price":"1200","priceCn":"","totalPrice":"1200000","totalPriceCn":"","remark":"","leftCount":"","status":"0","purchaseType":"","specification":"GB20241012-0001","specificationId":"1844934395131637761","materialCode":"HW009002004001","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","brand":"1821742140835680258","brandName":"小米","insertTime":"2024-12-05 11:31:44","insertPersonName":"集采中心负责人","tpPurchaseNeedMaterialId":"${needMaterialId2}","customIndex":"1"}]}</t>
-  </si>
-  <si>
-    <t>财务审批</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>财务登录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"fntoken": "$.data.access_token"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"Authorization": "Bearer ${fntoken}","identityRole":"IdentityRole_1"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"FinanceAdmin","password":"XVlt9SRJO6CRH6NI47q8_2SYucBY_mCSbq4iv9GCAFeQn3QPqT182jTT21DAhSLt/KyOK0ZuUFMXCSZ7TBtwOCetrX8p6tymmjVJ1xW5E6jCVWtMNxkWbB1qza6AXh5JMQDILaUgOJy6HPIMntHjVsVnsx/8yAvY0u1k_OrgdLg=","identity": "1"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"LegalAdmin","password":"aCAiGEy1QxrsIKWL0mgdVxljSI3w3AJ__mtO4sU4BnxfKpEuk69nGIKseIehsS7EH5wvHd5q3OQUwXYMqSk7HcO1Rlc0l6NruU8hDrMtD9FUOa_ucSDiPOZh9InD01BpbLHzcGTHJy94cV0I0J3Hl5zBn5usxKYzDwEklqv1AyY=","identity": "1"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"lgtoken": "$.data.access_token"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"Authorization": "Bearer ${lgtoken}","identityRole":"IdentityRole_1"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>采购预算总经理审批</t>
   </si>
   <si>
     <t>总经理登录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"sdTenderAdmin","password":"Obs1kyIloIlfmBM7VY_ynwKA_p_RvFA/yr9k6_25/s7KperJ7Tbl6ArwduNotBBTeK1gL4JUhHfSooDMV4a1L7HoBNzf3Ji/cpwoXyMLQZvCNgYnk_w/or3c9RSsDEsexgAfhpay9nyVAOMuS_H1pJgqKqbw3PBMYg0e7HsqAcc=","identity": "1"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"admintoken": "$.data.access_token"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"Authorization": "Bearer ${admintoken}","identityRole":"IdentityRole_1"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建采购需求</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tpPurchaseGov?submit=true</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>查看采购计划详情</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tpPurchasePlan/${planId}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"childPlanId1":"$.data.zlist.value[0].id","childPlanId2":"$.data.zlist.value[1].id"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>查询标段信息</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询需求信息</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tpPurchaseGov/page?busProjectType=2&amp;purchaseProjectName=${purchaseProjectNameDecode}&amp;current=1&amp;size=10&amp;total=166</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"tpId":"$.data.list[0].id"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/section/page?tpId=${tpId}&amp;tpType=2&amp;current=1&amp;size=10&amp;total=2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"busProjectType":"2","projectName":"${purchaseProjectName}","purchaseProjectName":"${purchaseProjectName}","purchaseMode":"6","pqrMode":"2","tenderOrganizeForm":"1","paNameAndPaCode":"","paName":"","paCode":"","ifDirectly":"true","inviteType":"1","transactionCenter":"顺德集团","typeAttachment":[],"sectionList":[{"bidSectionDesc":"${purchaseProjectName}-标段01","bidderCondition":"测试","ifSignUpApprove":"false","winBidServiceCharge":"1000","bidSectionName":"${purchaseProjectName}-标段01","bidLimitpriceHighest":"100","signUpFileList":[],"customId":"95491733537636759","bidSectionCode":"-","needMaterialList":[{"id":"${childPlanId1}","sectionId":"","planName":"","planId":"${planId}","tpPurchaseNeedId":"${needId}","tpPurchaseNeedMaterialId":"${needMaterialId1}","tpPurchaseNeedName":"","classifyName":"感冒灵","classifyCode":"HW009002004","classifyId":"1844932356959940610","materialId":"1844934129661554689","materialName":"999感冒灵","materialCount":"1000","unit":"箱","planUseTime":"","price":"1000","priceCn":"","totalPrice":"1000000","totalPriceCn":"","remark":"","leftCount":"","status":"0","purchaseType":"","specification":"GB20240912-001","specificationId":"1844934521673789442","materialCode":"HW009002004001","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","needType":"","insertTime":"2024-12-05 11:31:44","next":"","brand":"1821742140835680258","brandName":"小米","fenStatus":"","financeStatus":"","bossStatus":"","insertPersonName":"集采中心负责人"}]},{"bidSectionDesc":"${purchaseProjectName}-标段02","bidderCondition":"测试","ifSignUpApprove":"false","winBidServiceCharge":"2000","bidSectionName":"${purchaseProjectName}-标段02","bidLimitpriceHighest":"120","signUpFileList":[],"customId":"43911733537655350","bidSectionCode":"-","needMaterialList":[{"id":"${childPlanId2}","sectionId":"","planName":"","planId":"${planId}","tpPurchaseNeedId":"${needId}","tpPurchaseNeedMaterialId":"${needMaterialId2}","tpPurchaseNeedName":"","classifyName":"感冒灵","classifyCode":"HW009002004","classifyId":"1844932356959940610","materialId":"1844934129661554689","materialName":"999感冒灵","materialCount":"1000","unit":"箱","planUseTime":"","price":"1200","priceCn":"","totalPrice":"1200000","totalPriceCn":"","remark":"","leftCount":"","status":"0","purchaseType":"","specification":"GB20241012-0001","specificationId":"1844934395131637761","materialCode":"HW009002004001","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","needType":"","insertTime":"2024-12-05 11:31:44","next":"","brand":"1821742140835680258","brandName":"小米","fenStatus":"","financeStatus":"","bossStatus":"","insertPersonName":"集采中心负责人"}]}],"purchaserName":"河北顺恒集采中心有限公司","purchaserCode":"91130596MADHGFMC24","tenderGroupList":[{"name":"王菲","mobile":"13909310231","titleCode":"2010018","titleName":"教授","titleLevelCode":"1","titleLevelName":"初级","ifLeader":"true","customIndex":"0"}],"superviseGroupList":[],"projectId":"${planId}","projectType":"HW","purchaseProjectCode":"${needId}","regionCodeShowCus":[["13","1303","130304"]],"regionCodeShow":"[[\"13\",\"1303\",\"130304\"]]","regionCode":"130304","regionName":"河北省-秦皇岛市-北戴河区","fundingSource":"测试","projectOverview":"测试","purchaseContent":"测试","supervisionUnits":"[{\"userId\":\"1860239608462364672\",\"superviseUnitCode\":\"91130596MADHGFMC24\",\"superviseUnitName\":\"河北顺恒集采中心有限公司\",\"superviseUnitPhone\":\"15000000999\",\"contacts\":\"李三\",\"supervisoryAuthority\":\"测试监督部门\"}]"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"sectionId1":"$.data.list[0].id","bidSectionName1":"$.data.list[0].bidSectionName","sectionId2":"$.data.list[1].id","bidSectionName2":"$.data.list[1].bidSectionName","bidSectionCode1":"$.data.list[0].bidSectionCode","bidSectionCode2":"$.data.list[1].bidSectionCode"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tenderFile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"marginPrice":"1","marginUnit":"1","bidLimitpriceHighest":"100","bidLimitpriceUnit":"1","guaranteeTypeArr":[],"promiseLetterTemplateName":"","ifVerifyBasicAccount":"false","ifJudgesConfirmWinBidder":"false","ifSyndicatedFlag":"true","ifSupportSmallMicro":"true","ifSupportBlindBid":"false","ifDoubleEnvelope":"false","ifOpenCreditScoreReject":"false","bidOpeningType":"3","evaluationType":"1","ifOpenMeet":"false","perMargin":"1","perMarginUnit":"1","perMarginTypeArr":[],"ifSurvey":"false","ifRemote":"false","templateName":"","templateId":"","tfPrice":"123","payDesc":"无","paymentDate":"","vaildPeriod":"90","fileJmDuration":"10","tfName":"${bidSectionName1}","bidEvaluateRoom":"002","bidOpeningRoom":"101","fileQuestionEndTime":"${bidDocReferEndTime}","id":"${sectionId1}","bidSectionCode":"${bidSectionCode1}","bidSectionName":"${bidSectionName1}","tpName":"${purchaseProjectName}","insertTime":"2024-12-07 14:38:44","classifyCode":"","bidSectionId":"${sectionId1}","marginPayee":"河北顺恒集采中心有限公司","marginBank":"中国邮政储蓄银行股份有限公司邢台市襄都支行","marginAccount":"913055013000094327","guaranteeType":"4,6","perMarginPayee":"河北顺恒集采中心有限公司","perMarginBank":"中国邮政储蓄银行股份有限公司邢台市襄都支行","perMarginAccount":"913055013000094327","perMarginType":"4","tfPriceUnit":"元","tfPricePayee":"河北顺恒集采中心有限公司","tfPriceBank":"中国邮政储蓄银行股份有限公司邢台市襄都支行","tfPriceAccount":"913055013000094327","undefined":"","tpId":"${tpId}","bidOpeningPoint":"顺德集团"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tfCatalog?tfId=${tfid}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"id":"1865290536422531073","tfId":"${tfId}","envelope":"1","fieldName":"报价","fieldType":"1","fieldUnit":"万元","note":"","sortNum":"0","ifUppercase":"","ifRequired":"true","ifBidPrice":"true","bidPriceType":"0"},{"id":"1865290536443502593","tfId":"${tfId}","envelope":"1","fieldName":"供货周期","fieldType":"2","fieldUnit":"天","note":"","sortNum":"1","ifUppercase":"","ifRequired":"true","ifBidPrice":"false","bidPriceType":"1"}]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"methodName":"10","scorePrincipleType":"0","scorePrincipleParam":"计算所有评委评分，汇总全部评分后，计算评分均值","evalReportTemplateKey":"1779676938369970178","basicInfo":"{\"scoreComposeParam\":{\"priceScore\":30,\"technologyScore\":70,\"businessScore\":0,\"ruleContent\":\"本项目评标总分为100分，商务得分（报价得分): 30分，技术分70分\"}}","tfId":"${tfId}","ifNeedTecFile":"false","steps":[{"sortNum":"1","stepType":"1","scoreType":"1","stepName":"大","ifReject":"0","ifPqr":"false","pqrType":"","standardScore":"70","stepParam":"{\"standardScore\":70,\"rejectCondition\":{\"ruleContent\":\"\"},\"ifReject\":0}","isExpand":"false","items":[{"ifAbandoned":"false","itemMaxScore":"70","itemName":"阿达","itemStandard":"啊实打实大"}]},{"stepName":"报价得分","stepType":"2","standardScore":"30","stepParam":"{\"standardScore\":30,\"evaluationPriceRule\":{\"computeType\":1,\"computeName\":\"评标价计算\",\"standardName\":\"评标价\",\"computeMethod\":\"评标价=最低报价（包含修正后的报价）\",\"ruleContent\":\"以投标人投标报价或评标修正后报价，取最低报价为评标价\"},\"standardPriceRule\":{\"computeType\":1,\"computeName\":\"基准价计算\",\"standardName\":\"基准价\",\"computeMethod\":\"基准价=最低评标价\",\"ruleContent\":\"满足采购文件要求的最低评标价为评标基准价\"},\"quotationScoreRule\":{\"computeName\":\"报价得分计算\",\"standardName\":\"报价得分计算\",\"computeType\":1,\"computeMethod\":\"价格得分=（评标基准价/评标报价）*最高分\",\"ruleContent\":\"有效最低价为基准价，得最高分\"}}","sortNum":""}],"resultGatherModeParam":"{\"candidateParam\":{\"candidateType\":0,\"candidateNum\":3,\"recommendMethod\":\"汇总得分由高到低依次推荐 3 名 中标候选人。\",\"calibrateRule\":\"汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，中标人由招标人自行确定。\"},\"sortParam\":{\"sortType\":0,\"name\":\"汇总得分\",\"content\":\"汇总得分=报价得分+技术得分\",\"ruleContent\":\"-\"}}"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tfEvaluateMethod/setup</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tfDocTempItem/bathUpdate?ifNext=1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"fileId":"","fileName":"","fileType":9,"tfId":"${tfId}"}]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tenderFile/annex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tenderFile/saveAnnex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "tfId": "${tfId}"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>生成pdf</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"tfId":"$.data"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"tfId":"${tfId}","templateId":"1777150391619870721","bidMethodType":"10"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tfDocTemp/initTempItem</t>
-  </si>
-  <si>
-    <t>加密数据校验</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>get</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tenderFile/tfTar/${tfId}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[["操作成功!","==","$.msg","str"],[200,"==","$.code","int"]]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[["操作成功!","==","$.msg","str"],[200,"==","$.code","int"],["$.data.list[0].id","==","${sectionId1}","str"]]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[["操作成功!","==","$.msg","str"],[200,"==","$.code","int"],["$.data.list[0].id","==","${tpId}","str"]]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>select id as needId from sd_biz_trade_tender.tp_purchase_need t where t.purchase_need_name="${purchaseProjectName}";</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>生成加密数据包</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tenderFile/pack?id=${tfId}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>t提交招标文件</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tenderFile/submit?ifSubmit=true&amp;id=${tfId}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">update </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF000000"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>sd_biz_trade_tender</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF080808"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF000000"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t xml:space="preserve">tender_file t </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF0033B3"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t xml:space="preserve">set </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF000000"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF080808"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF871094"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>tender_file_signature</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF080808"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF067D17"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t xml:space="preserve">'1843843752338997249' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF0033B3"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t xml:space="preserve">where </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF000000"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF080808"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF871094"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>bid_section_id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF080808"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color rgb="FF067D17"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>'${sectionId1}'</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>etbtrade-tender/tfDocTemp/initTempItem</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>招标文件模板设置1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>招标文件模板设置2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>招标文件模板设置3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>file/file/query/list?replaceVisitEndpoint=http://minio.zszc.jianshicha.cn</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[${tfFileTempPdfId}]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"id":"${DocTempItems1}","insertPersonId":"1815283718319951872","insertPersonName":"集采中心负责人","insertTime":"2024-12-09 10:44:05","lastUpdatePersonId":"","lastUpdatePerson":"","lastUpdateTime":"2024-12-09 10:44:05","dataLevel":"","applyState":"","applyPersonName":"","applyPersonId":"","taskId":"","ifNeedApply":"","dataScopeUserId":"1815283718319951872","dataScopeDeptId":"10000-000257","tfId":"${tfId}","docId":"${docId}","tempId":"${DocTempItemsId1}","itemId":"1746835538786390018","itemEnKey":"BZRQ","itemChKey":"编制日期","itemKey":"BZRQ","itemVal":"2024-12-09","isRenderFrom":"true","fieldVariableVal":"{{BZRQ}}","labelType":"datepicker","tagAttribute":"(function(){\r\n  return {\r\n    format:'yyyy-MM-dd',\r\n    valueFormat:'yyyy-MM-dd',\r\n    rules:[\r\n      { required:true,message:'请选择编制日期',trigger:'change' }  \r\n    ],\r\n    timeType: 'date'\r\n  };\r\n})();"},{"id":"${DocTempItems2}","insertPersonId":"1815283718319951872","insertPersonName":"集采中心负责人","insertTime":"2024-12-09 10:44:05","lastUpdatePersonId":"","lastUpdatePerson":"","lastUpdateTime":"2024-12-09 10:44:05","dataLevel":"","applyState":"","applyPersonName":"","applyPersonId":"","taskId":"","ifNeedApply":"","dataScopeUserId":"1815283718319951872","dataScopeDeptId":"10000-000257","tfId":"${tfId}","docId":"${docId}","tempId":"1777150391619870721","itemId":"${DocTempItemsId2}","itemEnKey":"ZBRLXR","itemChKey":"招标人联系人","itemKey":"ZBRLXR","itemVal":"测试","isRenderFrom":"true","fieldVariableVal":"{{ZBRLXR}}","labelType":"input","tagAttribute":"(function(){\n  return {\n    rules:[\n      { required: true, message: '招标人联系人不能为空', trigger: 'blur' }\n    ]\n  };\n})();"},{"id":"${DocTempItems3}","insertPersonId":"1815283718319951872","insertPersonName":"集采中心负责人","insertTime":"2024-12-09 10:44:05","lastUpdatePersonId":"","lastUpdatePerson":"","lastUpdateTime":"2024-12-09 10:44:05","dataLevel":"","applyState":"","applyPersonName":"","applyPersonId":"","taskId":"","ifNeedApply":"","dataScopeUserId":"1815283718319951872","dataScopeDeptId":"10000-000257","tfId":"${tfId}","docId":"${docId}","tempId":"1777150391619870721","itemId":"${DocTempItemsId3}","itemEnKey":"ZBRLXDH","itemChKey":"招标人联系电话","itemKey":"ZBRLXDH","itemVal":"13900000001","isRenderFrom":"true","fieldVariableVal":"{{ZBRLXDH}}","labelType":"input","tagAttribute":"(function(){\n  return {\n    rules:[\n      { required: true, message: '招标人联系电话不能为空', trigger: 'blur' },\n      { required: true, message: '请填写正确的招标人联系电话', trigger: 'blur',pattern: /^1[3456789]\\d{9}$/ }\n    ],\n  };\n})();"},{"id":"${DocTempItems4}","insertPersonId":"1815283718319951872","insertPersonName":"集采中心负责人","insertTime":"2024-12-09 10:44:05","lastUpdatePersonId":"","lastUpdatePerson":"","lastUpdateTime":"2024-12-09 10:44:05","dataLevel":"","applyState":"","applyPersonName":"","applyPersonId":"","taskId":"","ifNeedApply":"","dataScopeUserId":"1815283718319951872","dataScopeDeptId":"10000-000257","tfId":"${tfId}","docId":"${docId}","tempId":"1777150391619870721","itemId":"${DocTempItemsId4}","itemEnKey":"ZBRYXDZ","itemChKey":"招标人邮箱地址","itemKey":"ZBRYXDZ","itemVal":"lucasneil0143@gmail.com","isRenderFrom":"true","fieldVariableVal":"{{ZBRYXDZ}}","labelType":"input","tagAttribute":"(function(){\n  return {\n    rules:[\n      { required: true, message: '招标人邮箱地址不能为空', trigger: 'blur' },\n      { required: true, message: '请填写正确的招标人邮箱地址', trigger: 'blur',pattern: /^([a-zA-Z0-9_-])+@([a-zA-Z0-9_-])+(.[a-zA-Z0-9_-])+/ }\n    ]\n  };\n})();"},{"id":"${DocTempItems5}","insertPersonId":"1815283718319951872","insertPersonName":"集采中心负责人","insertTime":"2024-12-09 10:44:05","lastUpdatePersonId":"","lastUpdatePerson":"","lastUpdateTime":"2024-12-09 10:44:05","dataLevel":"","applyState":"","applyPersonName":"","applyPersonId":"","taskId":"","ifNeedApply":"","dataScopeUserId":"1815283718319951872","dataScopeDeptId":"10000-000257","tfId":"${tfId}","docId":"${docId}","tempId":"1777150391619870721","itemId":"${DocTempItemsId5}","itemEnKey":"DJJZSJ","itemChKey":"递交投标文件截止时间","itemKey":"DJJZSJ","itemVal":"${docGetEndTime}","isRenderFrom":"true","fieldVariableVal":"{{DJJZSJ}}","labelType":"datepicker","tagAttribute":"(function(){\n  return {\n    format:'yyyy-MM-dd HH:mm',\n    valueFormat:'yyyy-MM-dd HH:mm:ss',\n    rules:[\n      { required:true,message:'请选择递交投标文件截止时间',trigger:'change' }  \n    ],\n    timeType: 'datetime',\n    pickerOptions: {\n      disabledDate(time) {\n         return time.getTime() &lt; Date.now() - 8.64e7;\n      }\n    }\n  };\n})();"},{"id":"${DocTempItems6}","insertPersonId":"1815283718319951872","insertPersonName":"集采中心负责人","insertTime":"2024-12-09 10:44:05","lastUpdatePersonId":"","lastUpdatePerson":"","lastUpdateTime":"2024-12-09 10:44:05","dataLevel":"","applyState":"","applyPersonName":"","applyPersonId":"","taskId":"","ifNeedApply":"","dataScopeUserId":"1815283718319951872","dataScopeDeptId":"10000-000257","tfId":"${tfId}","docId":"${docId}","tempId":"1777150391619870721","itemId":"${DocTempItemsId6}","itemEnKey":"ZBKSSJ","itemChKey":"获取招标文件开始时间","itemKey":"ZBKSSJ","itemVal":"${noticeSendTime}","isRenderFrom":"true","fieldVariableVal":"{{ZBKSSJ}}","labelType":"datepicker","tagAttribute":"(function(){\n  return {\n    format:'yyyy-MM-dd HH:mm',\n    valueFormat:'yyyy-MM-dd HH:mm:ss',\n    rules:[\n      { required:true,message:'请选择获取招标文件开始时间',trigger:'change' }  \n    ],\n    timeType: 'datetime'\n  };\n})();"},{"id":"${DocTempItems7}","insertPersonId":"1815283718319951872","insertPersonName":"集采中心负责人","insertTime":"2024-12-09 10:44:05","lastUpdatePersonId":"","lastUpdatePerson":"","lastUpdateTime":"2024-12-09 10:44:05","dataLevel":"","applyState":"","applyPersonName":"","applyPersonId":"","taskId":"","ifNeedApply":"","dataScopeUserId":"1815283718319951872","dataScopeDeptId":"10000-000257","tfId":"${tfId}","docId":"${docId}","tempId":"1777150391619870721","itemId":"${DocTempItemsId7}","itemEnKey":"ZBJSSJ","itemChKey":"获取招标文件结束时间","itemKey":"ZBJSSJ","itemVal":"${docGetEndTime}","isRenderFrom":"true","fieldVariableVal":"{{ZBJSSJ}}","labelType":"datepicker","tagAttribute":"(function(){\n  return {\n    format:'yyyy-MM-dd HH:mm',\n    valueFormat:'yyyy-MM-dd HH:mm:ss',\n    rules:[\n      { required:true,message:'请选择获取招标文件结束时间',trigger:'change' }  \n    ],\n    timeType: 'datetime',\n    pickerOptions: {\n      disabledDate(time) {\n        return time.getTime() &lt; Date.now() - 8.64e7;\n      }\n    }\n  };\n})();"},{"id":"${DocTempItems8}","insertPersonId":"1815283718319951872","insertPersonName":"集采中心负责人","insertTime":"2024-12-09 10:44:05","lastUpdatePersonId":"","lastUpdatePerson":"","lastUpdateTime":"2024-12-09 10:44:05","dataLevel":"","applyState":"","applyPersonName":"","applyPersonId":"","taskId":"","ifNeedApply":"","dataScopeUserId":"1815283718319951872","dataScopeDeptId":"10000-000257","tfId":"${tfId}","docId":"${docId}","tempId":"1777150391619870721","itemId":"${DocTempItemsId8}","itemEnKey":"JHDD","itemChKey":"交货地点","itemKey":"JHDD","itemVal":"测试服打发斯蒂芬第三方代发都发啥打法","isRenderFrom":"true","fieldVariableVal":"{{JHDD}}","labelType":"input","tagAttribute":"(function(){\n  return {\n    rules:[\n      { required: true, message: '交货地点不能为空', trigger: 'blur' }\n    ]\n  };\n})();"}]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"tfId": "${tfId}"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"tfFileTempPdfId":"$.data.tfFileTempPdfId","docId":"$.data.id","DocTempItems1":"$.data.tfDocTempItems[0].id","DocTempItemsId1":"$.data.tfDocTempItems[0].itemId","DocTempItems2":"$.data.tfDocTempItems[1].id","DocTempItemsId2":"$.data.tfDocTempItems[1].itemId","DocTempItems3":"$.data.tfDocTempItems[2].id","DocTempItemsId3":"$.data.tfDocTempItems[2].itemId","DocTempItems4":"$.data.tfDocTempItems[3].id","DocTempItemsId4":"$.data.tfDocTempItems[3].itemId","DocTempItems5":"$.data.tfDocTempItems[4].id","DocTempItemsId5":"$.data.tfDocTempItems[4].itemId","DocTempItems6":"$.data.tfDocTempItems[5].id","DocTempItemsId6":"$.data.tfDocTempItems[5].itemId","DocTempItems7":"$.data.tfDocTempItems[6].id","DocTempItemsId7":"$.data.tfDocTempItems[6].itemId","DocTempItems8":"$.data.tfDocTempItems[7].id","DocTempItemsId8":"$.data.tfDocTempItems[7].itemId",}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>提交采购公告</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tenderBulletin?submit=true</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>初始化公告</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tenderBulletin/getSectionList?proId=${tpId}&amp;sectionType=2&amp;bulletinType=4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"noticeContentId":"$.data[0].tempFileId"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"noticeNature":"0","openType":"0","bulletinType":"4","bidDocReferMethod":"1","tenderDocGetMethod":"1","sectionIds":"${sectionId1}","challengeCall":"16603190317","templateBidId":"","bulletinDuty":"","bulletinDutyCodeType":"97","bulletinDutyCode":"91130596MADHGFMC24","tenderProName":"${purchaseProjectName}","ifSyndicatedFlag":"false","technicalRequirements":"/","implementPolicy":"/","noticeContent":"${noticeContentId}","noticeName":"${purchaseProjectName}","noticeSendTime":"","noticeEndTime":"","docGetStartTime":"${noticeSendTime}","docGetEndTime":"${noticeEndTime}","bidDocReferEndTime":"${noticeEndTime}","sectionType":"2","tenderProId":"${tpId}","tenderProCode":"${needId}","tenderProType":"2","tradeCenterName":"顺德集团","tradeCenterCode":"null","regionCode":"130304","regionName":"河北省-秦皇岛市-北戴河区","bidMode":"6","tenderLxr":"河北顺恒集采中心有限公司","bidOpenAddr":"顺德集团","bidOpenTime":"${noticeEndTime}","hostId":"1814243161552375808","hostName":"张聚平","hostOrgId":"10000-000257","hostTelephone":"16603190317"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>select t.id as bulletinId from sd_biz_trade_tender.tender_bulletin t where t.tender_pro_code='${needId}';</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>flowable/task/complete</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"comment":"","taskLocalVariables":{"approveFiles":""},"businessKey":"${bulletinId}","processVariables":{}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>公告审批</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>发布公告</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade-tender/tenderBulletin/submit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{ "id": "${bulletinId}"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>update sd_biz_open_eval.tp_open_section t set t.open_start_time=DATE_ADD(NOW(), interval 20 minute) where t.section_id='${sectionId1}';update sd_biz_open_eval.tp_open_org t set t.open_start_time=DATE_ADD(NOW(), interval 20 minute) where t.section_id='${sectionId1}';</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{"token": "$.data.access_token"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"${sdadmin}","password":"${sdpassword}","identity": "1"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>法务1登录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>法务1审批</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>法务2登录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>法务2审批</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"langyun13","password":"f7Fw5NRihUnJXQJnVj_0OYOkfXuf/ZtXJen9K3BLQ6/4u0ufZRm7/krp04bsfpswssvj9ow6_RY0Kfco_Ken2HAF/leL4st0UbAziIiBwCx3pLS/XnLmgmvSjLgSt4rxAgGZQ8naBgjOiZnULZpHQuygaoXEJ8wl0KLiwOVSVMM=","identity": "1"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"username":"${username}","password":"${password}","identity": "1"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>brace/tpPurchaseNeed?submit=true</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>brace/tpPurchaseNeed/page?taskStatus=1&amp;current=1&amp;size=10&amp;total=5&amp;purchaseNeedName=${purchaseProjectNameDecode}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>brace/tpPurchaseNeed/${needId}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>brace/tpPurchasePlan?submit=true</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>brace/tpPurchasePlan/page?taskStatus=1&amp;planName=${purchaseProjectNameDecode}&amp;current=1&amp;size=10&amp;total=294</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>brace/tpPurchasePlan/${planId}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建采购项目</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询项目信息</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"busProjectType":"2","paName":"","paCode":"","pqrMode":"${pqrMode}","paNameAndPaCode":"","ifRequiredTender":"true","ifPpp":"false","ifEEvaluation":"true","ifReserveField":"false","ifPushProvincePsp":"true","ifPushChinaPublicService":"true","investCodeType":"","tenderOrganizeForm":"${tenderOrganizeForm}","typeAttachment":[],"contributiveRatio":[],"sectionList":[{"bidSectionDesc":"${purchaseProjectName}-标段01","bidderCondition":"${purchaseProjectName}-标段01","ifSignUpApprove":"false","bidSectionName":"${purchaseProjectName}-标段01","CutCus":[],"classifyCodeCus":["B","B01","B0101","B010101"],"classifyCode":"B-B01-B0101-B010101","classifyName":"货物类-机械、设备类-建筑机械-盾构设备","investBudget":"34","customId":"12431740013087698","bidSectionCode":"-","needMaterialList":[{"id":"${childPlanId1}","sectionId":"","planName":"","planId":"${planId}","tpPurchaseNeedId":"${needId}","tpPurchaseNeedMaterialId":"${needMaterialId1}","tpPurchaseNeedName":"","classifyName":"感冒灵","classifyCode":"HW009002004","classifyId":"1844932356959940610","materialId":"1844934129661554689","materialName":"999感冒灵","materialCount":"1000","unit":"箱","planUseTime":"","price":"1000","priceCn":"","totalPrice":"1000000","totalPriceCn":"","remark":"","leftCount":"","status":"0","purchaseType":"","specification":"GB20240912-001","specificationId":"1844934521673789442","materialCode":"HW009002004001","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","needType":"","insertTime":"2024-12-05 11:31:44","next":"","brand":"1821742140835680258","brandName":"小米","fenStatus":"","financeStatus":"","bossStatus":"","insertPersonName":"集采中心负责人"}]},{"bidSectionDesc":"${purchaseProjectName}-标段02","bidderCondition":"${purchaseProjectName}-标段02","ifSignUpApprove":"false","bidSectionName":"${purchaseProjectName}-标段02","CutCus":[],"classifyCodeCus":["B","B01","B0101","B010101"],"classifyCode":"B-B01-B0101-B010101","classifyName":"货物类-机械、设备类-建筑机械-盾构设备","investBudget":"134","customId":"12431740013087698","bidSectionCode":"-","needMaterialList":[{"id":"${childPlanId2}","sectionId":"","planName":"","planId":"${planId}","tpPurchaseNeedId":"${needId}","tpPurchaseNeedMaterialId":"${needMaterialId2}","tpPurchaseNeedName":"","classifyName":"感冒灵","classifyCode":"HW009002004","classifyId":"1844932356959940610","materialId":"1844934129661554689","materialName":"999感冒灵","materialCount":"1000","unit":"箱","planUseTime":"","price":"1200","priceCn":"","totalPrice":"1200000","totalPriceCn":"","remark":"","leftCount":"","status":"0","purchaseType":"","specification":"GB20241012-0001","specificationId":"1844934395131637761","materialCode":"HW009002004001","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","needType":"","insertTime":"2024-12-05 11:31:44","next":"","brand":"1821742140835680258","brandName":"小米","fenStatus":"","financeStatus":"","bossStatus":"","insertPersonName":"集采中心负责人"}]}],"purchaseProjectName":"${purchaseProjectName}","transactionCenterCode":"001","regionCodeShowCus":[["13","1301","130102"]],"regionCodeShow":"[[\"13\",\"1301\",\"130102\"]]","regionCode":"130102","regionName":"河北省-石家庄市-长安区","budget":344,"unitBudget":"1","priceFrom":"1","priceDiscountRate":"","industriesTypeCus":["B","B06"],"industriesType":"B-B06","industriesTypeName":"采矿业-煤炭开采和洗选业","purchaseOrganizeForm":"2","projectType":"HW","purchaseMode":"${purchaseMode}","budgetDepartmentUnitType":"1","purchaseContent":"测试","purchaserLxr":"测试","purchaserLxrTelephone":"13000000001","contacts":"监督人","superviseUnitName":"河北顺德投资集团资产管理有限公司","superviseUnitCode":"911305005881850417","superviseUnitPhone":"13773156156","ifDirectly":"false","supervisionUnits":"[{\"contacts\":\"监督人\",\"superviseUnitCode\":\"911305005881850417\",\"superviseUnitName\":\"河北顺德投资集团资产管理有限公司\",\"superviseUnitPhone\":\"13773156156\"}]","investDetail":[{"investName":"采购单位","investCode":"2","investRatio":"100"}],"transactionCenter":"测试交易中心"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"id":"","formTemplateId":"","fieldName":"报价","fieldType":1,"bidPriceType":0,"quotationType":"","fieldUnit":"万元","ifRequired":"true","envelope":"","note":"","autoAddCapital":"","ifBidPrice":"true","sortNum":"","tfId":"${tfId}"},{"id":"","formTemplateId":"","fieldName":"工期","fieldType":1,"bidPriceType":1,"quotationType":"","fieldUnit":"天","ifRequired":"false","envelope":"","note":"","autoAddCapital":"","ifBidPrice":"false","sortNum":"","tfId":"${tfId}"}]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Authorization": "Bearer ${token}","identityRole":"IdentityRole_1"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>file-cloud/file/upload/resume/chunk</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"attachmentTenderFile":"$.data.id"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>etbtrade-tender/tfDocTempItem/bathUpdateUpload</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ifUpload":1,"ifNext":1,"attachmentTenderFile":"${attachmentTenderFile}","tfId":"${tfId}","tfGroupId":"${tfGroupId}","tenderFileWord":"","tenderFileSignature":""}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"fileId":"","fileName":"","fileType":9,"tfId":"${tfId}","tfGroupId":"${tfGroupId}"}]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>etbtrade-tender/tenderFile/pack?tfGroupId=${tfGroupId}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"username":"${firstAprUser}","password":"${firstAprPsw}","identity": "1"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Aprtoken": "$.data.access_token"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Authorization": "Bearer ${Aprtoken}","identityRole":"IdentityRole_1"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询招标公告</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"bulletinId":"$.data.[0].bulletinId"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>a5</t>
+  </si>
+  <si>
+    <t>a22</t>
+  </si>
+  <si>
+    <t>a26</t>
+  </si>
+  <si>
+    <t>a29</t>
+  </si>
+  <si>
+    <t>a30</t>
+  </si>
+  <si>
+    <t>a31</t>
+  </si>
+  <si>
+    <t>a32</t>
+  </si>
+  <si>
+    <t>a33</t>
+  </si>
+  <si>
+    <t>{"needMaterialId1":"$.data.needMaterialList[0].id","needMaterialId2":"$.data.needMaterialList[1].id"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"userId":"1814243161552375808","userName":"张聚平","needType":"1816456766428397569","needContent":"","departmentName":"河北顺恒集采中心有限公司","departmentId":"10000-000257","purchaseCatalog":"HW","purchaseNeedName":"${purchaseProjectName}","needMaterialList":[{"skuId":"1892748710053134338","skuParam":"","classifyId":"1816456766428397569","classifyCode":"HW009001001","classifyName":"消毒类药剂","materialId":"1892748314475741186","materialCode":"HW009001001006","materialName":"百步酊","measureUnit":"桶","brandName":"晨光","brand":"1892747897335431169","specification":"HK00101","price":"9999","specificationId":"1892748710053134338","unit":"桶","customIndex":"0","materialCount":"422","totalPrice":"4219578"},{"skuId":"1892748772321771522","skuParam":"","classifyId":"1816456766428397569","classifyCode":"HW009001001","classifyName":"消毒类药剂","materialId":"1892748097407926274","materialCode":"HW009001001005","materialName":"酒精89","measureUnit":"瓶","brandName":"晨光","brand":"1892747897335431169","specification":"JJ89","price":"450","specificationId":"1892748772321771522","unit":"瓶","customIndex":"1","materialCount":"200","totalPrice":"90000"}]}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"totalPrice":"4309578","bigTotalPrice":"肆佰叁拾万玖仟伍佰柒拾捌元整","remark":"测试","fileIds":"","proType":"2","needMaterialList":[],"purchaseType":"${purchaseMode}","planName":"${purchaseProjectName}","materialType":"HW","linkman":"测试","linkmanTel":"13000000001","infoMaterialList":[{"tpPurchaseNeedId":"${needId}","classifyName":"消毒类药剂","classifyCode":"HW009001001","classifyId":"1816456766428397569","materialId":"1892748097407926274","materialName":"酒精89","materialCount":200,"unit":"瓶","planUseTime":"","price":450,"priceCn":"","totalPrice":90000,"totalPriceCn":"","remark":"","leftCount":"","status":0,"purchaseType":"","specification":"JJ89","specificationId":"1892748772321771522","materialCode":"HW009001001005","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","brand":"1892747897335431169","brandName":"晨光","insertTime":"2025-02-21 09:32:22","insertPersonName":"张聚平","tpPurchaseNeedMaterialId":"${needMaterialId1}","customIndex":"0"},{"tpPurchaseNeedId":"${needId}","classifyName":"消毒类药剂","classifyCode":"HW009001001","classifyId":"1816456766428397569","materialId":"1892748314475741186","materialName":"百步酊","materialCount":422,"unit":"桶","planUseTime":"","price":9999,"priceCn":"","totalPrice":4219578,"totalPriceCn":"","remark":"","leftCount":"","status":0,"purchaseType":"","specification":"HK00101","specificationId":"1892748710053134338","materialCode":"HW009001001006","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","brand":"1892747897335431169","brandName":"晨光","insertTime":"2025-02-21 09:32:22","insertPersonName":"张聚平","tpPurchaseNeedMaterialId":"${needMaterialId2}","customIndex":"1"}]}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"busProjectType":"2","paName":"","paCode":"","pqrMode":"${pqrMode}","paNameAndPaCode":"","ifRequiredTender":"true","ifPpp":"false","ifEEvaluation":"true","ifReserveField":"false","ifPushProvincePsp":"true","ifPushChinaPublicService":"true","investCodeType":"","tenderOrganizeForm":"${tenderOrganizeForm}","typeAttachment":[],"contributiveRatio":[],"sectionList":[{"bidSectionName":"${purchaseProjectName}-标段01","bidSectionDesc":"${purchaseProjectName}-标段01","bidderCondition":"${purchaseProjectName}-标段01","ifSignUpApprove":"false","CutCus":[{"id":"${childPlanId1}","purchasePlanMaterialId":"${childPlanId1}","planName":"","planId":"${planId}","tpPurchaseNeedId":"${needId}","tpPurchaseNeedMaterialId":"${needMaterialId1}","tpPurchaseNeedName":"","classifyName":"消毒类药剂","classifyCode":"HW009001001","classifyId":"1816456766428397569","materialId":"1892748097407926274","materialName":"酒精89","materialCount":200,"unit":"瓶","planUseTime":"","price":450,"priceCn":"","totalPrice":90000,"totalPriceCn":"","remark":"","leftCount":"","status":0,"purchaseType":"","specification":"JJ89","specificationId":"1892748772321771522","materialCode":"HW009001001005","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","needType":"","insertTime":"2025-02-21 09:32:22","brand":"1892747897335431169","brandName":"晨光","fileIds":"","purchaseCatalog":"HW","planTotalPrice":4309578,"needContent":""}],"classifyCodeCus":["B","B02","B0201","B020129"],"classifyCode":"B-B02-B0201-B020129","classifyName":"货物类-医疗器械-医疗器械-介入器材","investBudget":"2000","signUpFileList":[],"customId":"93741740102027603","bidSectionCode":"-","needMaterialList":[{"id":"${childPlanId1}","purchasePlanMaterialId":"${childPlanId1}","planName":"","planId":"${planId}","tpPurchaseNeedId":"${needId}","tpPurchaseNeedMaterialId":"${needMaterialId1}","tpPurchaseNeedName":"","classifyName":"消毒类药剂","classifyCode":"HW009001001","classifyId":"1816456766428397569","materialId":"1892748097407926274","materialName":"酒精89","materialCount":200,"unit":"瓶","planUseTime":"","price":450,"priceCn":"","totalPrice":90000,"totalPriceCn":"","remark":"","leftCount":"","status":0,"purchaseType":"","specification":"JJ89","specificationId":"1892748772321771522","materialCode":"HW009001001005","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","needType":"","insertTime":"2025-02-21 09:32:22","brand":"1892747897335431169","brandName":"晨光","fileIds":"","purchaseCatalog":"HW","planTotalPrice":4309578,"needContent":""}]},{"bidSectionName":"${purchaseProjectName}-标段02","bidSectionDesc":"${purchaseProjectName}-标段02","bidderCondition":"${purchaseProjectName}-标段02","ifSignUpApprove":"false","CutCus":[{"id":"${childPlanId2}","purchasePlanMaterialId":"${childPlanId2}","planName":"","planId":"${planId}","tpPurchaseNeedId":"${needId}","tpPurchaseNeedMaterialId":"${needMaterialId2}","tpPurchaseNeedName":"","classifyName":"消毒类药剂","classifyCode":"HW009001001","classifyId":"1816456766428397569","materialId":"1892748314475741186","materialName":"百步酊","materialCount":422,"unit":"桶","planUseTime":"","price":9999,"priceCn":"","totalPrice":4219578,"totalPriceCn":"","remark":"","leftCount":"","status":0,"purchaseType":"","specification":"HK00101","specificationId":"1892748710053134338","materialCode":"HW009001001006","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","needType":"","insertTime":"2025-02-21 09:32:22","brand":"1892747897335431169","brandName":"晨光","fileIds":"","purchaseCatalog":"HW","planTotalPrice":4309578,"needContent":""}],"classifyCodeCus":["B","B02","B0201","B020102"],"classifyCode":"B-B02-B0201-B020102","classifyName":"货物类-医疗器械-医疗器械-注射穿刺器械","investBudget":"5000","signUpFileList":[],"customId":"32891740102049572","bidSectionCode":"-","needMaterialList":[{"id":"${childPlanId2}","purchasePlanMaterialId":"${childPlanId2}","planName":"","planId":"${planId}","tpPurchaseNeedId":"${needId}","tpPurchaseNeedMaterialId":"${needMaterialId2}","tpPurchaseNeedName":"","classifyName":"消毒类药剂","classifyCode":"HW009001001","classifyId":"1816456766428397569","materialId":"1892748314475741186","materialName":"百步酊","materialCount":422,"unit":"桶","planUseTime":"","price":9999,"priceCn":"","totalPrice":4219578,"totalPriceCn":"","remark":"","leftCount":"","status":0,"purchaseType":"","specification":"HK00101","specificationId":"1892748710053134338","materialCode":"HW009001001006","departmentId":"10000-000257","departmentName":"河北顺恒集采中心有限公司","userName":"","needType":"","insertTime":"2025-02-21 09:32:22","brand":"1892747897335431169","brandName":"晨光","fileIds":"","purchaseCatalog":"HW","planTotalPrice":4309578,"needContent":""}]}],"planId":"${planId}","purchasePlanCode":"${planId}","purchasePlanName":"测试","purchaserLxr":"测试","purchaserLxrTelephone":"13000000001","purchaseMode":"${purchaseMode}","projectType":"D01","purchaseProjectType":"D01","purchaseProjectName":"${purchaseProjectName}","transactionCenterCode":"001","regionCodeShowCus":[["13","1301","130102"]],"regionCodeShow":"[[\"13\",\"1301\",\"130102\"]]","regionCode":"130102","regionName":"河北省-石家庄市-长安区","priceFrom":"1","priceDiscountRate":"","budget":9899,"unitBudget":"1","industriesTypeCus":["A","A01"],"industriesType":"A-A01","industriesTypeName":"农、林、牧、渔业-农业","purchaseOrganizeForm":"2","budgetDepartmentUnitType":"2","contacts":"监督人","superviseUnitName":"河北顺德投资集团资产管理有限公司","superviseUnitCode":"911305005881850417","superviseUnitPhone":"13773156156","ifDirectly":"false","supervisionUnits":"[{\"contacts\":\"监督人\",\"superviseUnitCode\":\"911305005881850417\",\"superviseUnitName\":\"河北顺德投资集团资产管理有限公司\",\"superviseUnitPhone\":\"13773156156\"}]","investDetail":[{"investName":"采购单位","investCode":"2","investRatio":"100"}],"transactionCenter":"测试交易中心"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询catalogId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"methodName":"10","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","scorePrincipleType":0,"scaleProcess":"","ifOfferRank":"false","ifWeight":"false","creditScoreParam":"{}","ifCreditScore":"false","creditWeight":"","ifCreditWeight":"false","ifPqrParam":"true","tfId":"${tfId}","tfGroupId":"${tfGroupId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"isExpand":"false","stepName":"测试","sort":1,"stepType":0,"pqrType":0,"items":[{"itemName":"测试","itemStandard":"测试","ifAbandoned":"true"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":1,"ifReject":"false","ifBlindBid":"false","rejectType":1,"isExpand":"false","stepName":"技术","sort":2,"stepType":1,"standardScore":70,"catalogId":"","items":[{"itemMinScore":22,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":1,\"rejectCondition\":{\"ruleContent\":\"\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1,\"ifReject\":0}"},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"isExpand":"false","stepName":"报价","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"${catalogId}\",\"standardPriceRule\":{\"computeName\":\"基准价计算\",\"computeType\":1,\"standardName\":\"系统计算\",\"computeMethod\":\"\",\"computeMode\":2,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"computeName\":\"报价得分计算\",\"standardName\":\"低价优先法\",\"computeType\":1,\"ruleContent\":\"以有效最低价为基准价，得最高分Fmax，计算公式：价格得分=（评标基准价/评标报价）*最高分\",\"computeMethod\":\"以有效最低价为基准价，得最高分Fmax，计算公式：价格得分=（评标基准价/评标报价）*最高分\"}}"}],"resultGatherModeParam":"{\"candidateParam\":{\"candidateType\":0,\"candidateNum\":3,\"recommendMethod\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，中标人由招标人自行确定。\",\"calibrateRule\":\"汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，中标人由招标人自行确定。\"},\"sortParam\":{\"sortType\":0,\"name\":\"汇总得分\",\"content\":\"汇总得分=报价得分+技术得分\",\"ruleContent\":\"-\"}}","resultGatherModeDesc":"汇总得分 =  技术得分 + 价格得分"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"tfId":"$.data.id","tfGroupId":"$.data.tfGroupId"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"marginPrice":"1","marginUnit":"1","guaranteeTypeArr":[],"promiseLetterTemplateName":"","ifVerifyBasicAccount":"false","ifJudgesConfirmWinBidder":"${ifJudgesConfirmWinBidder}","ifShortlistedProject":"false","ifSyndicatedFlag":"${ifSyndicatedFlag}","ifSupportSmallMicro":"${ifSupportSmallMicro}","ifSupportBlindBid":"${ifSupportBlindBid}","ifSameSerialNum":"false","ifDoubleEnvelope":"false","tfSignReq":"3","encryptionWay":"password,CA01,EQ03","bidOpeningType":"3","evaluationType":"1","ifOpenMeet":"false","perMargin":"","perMarginUnit":"","perMarginTypeArr":[],"ifSurvey":"false","ifRemote":"false","templateName":"","templateId":"","tfPrice":"200","paymentDate":"","ifSecondPriceUp":1,"smallMicroType":2,"smallMicroContentFirst":"-","smallMicroContentSecond":"-","smallMicroContent":"22.00","vaildPeriod":90,"fileJmDuration":30,"tfName":"${purchaseProjectName}","address":"测试","fileQuestionEndTime":"${docGetEndTime}","sectionList":[{"bidLimitpriceHighest":2000,"bidLimitpriceUnit":1,"bidSectionId":"${sectionId1}","bidSectionName":"${bidSectionName1}","bidSectionCode":"${bidSectionCode1}"}],"marginPayee":"河北顺恒集采中心有限公司","marginBank":"中国邮政储蓄银行股份有限公司邢台市襄都支行","marginAccount":"913055013000094327","marginType":"4,3","tfPriceUnit":"0","tfPricePayee":"测试","tfPriceBank":"3453423423432","tfPriceAccount":"3423432423423","tfPriceType":"9","guaranteeType":"4,3","tpId":"${tpId}","tpName":"${purchaseProjectName}","bidOpeningPoint":"测试"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>etbtrade-tender/tfCatalog?tfId=${tfId}&amp;tfGroupId=${tfGroupId}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>etbtrade-tender/tfCatalog/bid/${tfId}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"catalogId":"$.data[0].id"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"urlResized":"","image":{},"isPlayingAv":"false","oldFileName":"","oldCustomName":"","upload":{"data":"","error":"false"},"lastKnownSrc":"","raw":{"status":"parsing"},"server":{"status":"parsing"},"file":{"status":"parsing"},"thumbnailSize":360,"read":"false","dimensions":{"width":0,"height":0},"error":"false","options":{"read":"","maxSize":"","accept":"","thumbnailSize":"","averageColor":"","withCredentials":""},"maxSize":"","accept":"","id":"0.8826872634463498:1740103604417","calculateAverageColor":"","fileSize":348843,"status":"uploading","fileMd5":"43390c888cdd9d2d688ba83826ed6448","fileSuffix":"application/pdf","chunkCount":1,"progress":0,"downloadProgress":0,"fileName":"投标文件正文.pdf","replaceVisitEndpoint":"http://minio.zszc.jianshicha.cn"}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"templateBidId":17,"COMBOSIGN":"0","REQUIREMENT":"详见招标文件","certificationCus":["APTITUDE","STANDBY17"],"certificationCusValue":[{"code":"APTITUDE","name":"资质要求"},{"code":"STANDBY17","name":"其他主要人员要求"}],"APTITUDE":"测试","STANDBY14":"","ACHIEVEMENT":"","STANDBY15":"","STANDBY16":"","STANDBY17":"测试","STANDBY18":"","STANDBY19":"","STANDBY25":"","bidDocReferStartTime":"","docGetEndTime":"${noticeEndTime}","STANDBY23":"1","SURVEYTIME":"","SURVEYPLACE":"","STANDBY24":"1","YBHTIME":"","YBHPLACE":"","METHOD":"1","TGXXSCNUM":"","XDTGZGYS":"","SFBC":"1","trafficShow":"1","tenderProName":"${purchaseProjectName}","WJDJFF":"阳光招采平台（http://www.jy.jiezhaowang.com）","bulletinMedia":"1749616762503266305","PLATFORMNAME":"","ZBR_ZIPCODE":"/","ZBDL_ZIPCODE":"/","zbrFax":"/","ZBDL_FAX":"/","ZBR_EMAIL":"/","ZBDL_EMAIL":"/","ZBR_WEBSITE":"/","ZBDL_WEBSITE":"/","ZBR_BANKNAME":"/","ZBDL_BANKNAME":"/","ZBR_ACCOUNT":"/","ZBDL_ACCOUNT":"/","JTGJ":"","noticeName":"${purchaseProjectName}","docGetEndTimeCus":"${noticeEndTime}","docGetStartTimeCus":"${noticeSendTime}","docGetStartTime":"${noticeSendTime}","bidOpenTimeCus":"${noticeEndTime}","bidDocReferEndTime":"${noticeEndTime}","HZJG":"测试","PWMC":"测试","YEZHU":"测试","ZJLY":"测试","CZBL":"测试","ZBR":"测试","STANDBY12":"测试","STANDBY13":"测试","bidOpenTime":"${noticeEndTime}","BIDPRICE":"200","DATADEPOSIT":"200","ZBR_NAME":"测试","ZBDL_NAME":"测试","ZBR_ADDRESS":"测试","ZBDL_ADDRESS":"测试","ZBR_CONTACTS":"测试","ZBDL_CONTACTS":"测试","ZBR_TEL":"13000000001","ZBDL_TEL":"13000000002","noticeNature":0,"openType":0,"bulletinType":4,"bidDocReferMethod":1,"tenderDocGetMethod":1,"sectionIds":"${sectionId1}","challengeCall":"16603190316","bulletinDuty":"","bulletinDutyCodeType":"97","bulletinDutyCode":"91130596MADHGFMC24","ifSyndicatedFlag":"false","technicalRequirements":"/","implementPolicy":"/","noticeContent":"&lt;div data-v-6f2b1efd=\"\" id=\"editorContent\" style=\"overflow-wrap: break-word; word-break: break-all; font-family: 微软雅黑;\"&gt;&lt;h3 data-v-6f2b1efd=\"\" class=\"\\&amp;quot;tit\\&amp;quot;\" style=\"text-align: center;\"&gt;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/h3&gt; &lt;h3 data-v-6f2b1efd=\"\" class=\"\\&amp;quot;tit\\&amp;quot;\"&gt;1.招标条件&lt;/h3&gt; &lt;div data-v-6f2b1efd=\"\" class=\"\\&amp;quot;context\\&amp;quot;\"&gt;&lt;p data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;本招标项目&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;&lt;/span&gt; （项目名称）已由&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; （项目审批、核准或备案机关名称）以 &lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; （批文名称及编号）批准建设，项目业主为&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; ，建设资金来自&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; （资金来源），项目出资比例为 &lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; ，招标人为&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; 。项目已具备招标条件，&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;现对该项目的设计施工总承包进行公开招标。&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;/div&gt; &lt;h3 data-v-6f2b1efd=\"\" class=\"\\&amp;quot;tit\\&amp;quot;\"&gt;2.项目概况与招标范围&lt;/h3&gt; &lt;p data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;&amp;nbsp;2.1 项目概况：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-6f2b1efd=\"\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp; 2.2 招标范围：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-6f2b1efd=\"\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;&amp;nbsp; &amp;nbsp;（&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;说明本次招标项目的建设地点、规模、计划工期、招标范围等&lt;/span&gt;）。&lt;/span&gt;&lt;/p&gt; &lt;h3 data-v-6f2b1efd=\"\" class=\"\\&amp;quot;tit\\&amp;quot;\"&gt;3.投标人资格要求&lt;/h3&gt; &lt;div data-v-6f2b1efd=\"\" class=\"\\&amp;quot;context\\&amp;quot;\"&gt;&lt;p data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp; &lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;3.1 本次招标对投标人的资格要求如下：\n      &lt;div data-v-6f2b1efd=\"\" class=\"content co-m-t-6 co-font-16\"&gt;&lt;div data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp;&amp;nbsp;&amp;nbsp; &lt;span data-v-6f2b1efd=\"\"&gt;3.1.1 资质要求: &lt;/span&gt; 测试； &lt;/div&gt;&lt;/div&gt;&lt;div data-v-6f2b1efd=\"\" class=\"content co-m-t-6 co-font-16\"&gt;&lt;div data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp;&amp;nbsp;&amp;nbsp; &lt;span data-v-6f2b1efd=\"\"&gt;3.1.2 其他主要人员要求: &lt;/span&gt; 测试； &lt;/div&gt;&lt;/div&gt;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-6f2b1efd=\"\"&gt;&lt;/p&gt;&lt;div data-v-6f2b1efd=\"\" class=\"co-font-16\"&gt;&amp;nbsp;&amp;nbsp;&amp;nbsp; 3.2 本次招标 不接受 （接受或不接受）联合体投标。&lt;!----&gt;&lt;/div&gt; &lt;p data-v-6f2b1efd=\"\"&gt;&lt;/p&gt;&lt;/div&gt; &lt;h3 data-v-6f2b1efd=\"\" class=\"\\&amp;quot;tit\\&amp;quot;\"&gt;4.招标文件的获取&lt;/h3&gt; &lt;div data-v-6f2b1efd=\"\" class=\"\\&amp;quot;context\\&amp;quot;\"&gt;&lt;p data-v-6f2b1efd=\"\"&gt;&lt;strong data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp; &lt;/strong&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;4.1 凡有意参加投标者，请于&amp;nbsp;&lt;span data-v-6f2b1efd=\"\"&gt;${noticeSendTime}&lt;/span&gt; 至&amp;nbsp;&lt;span data-v-6f2b1efd=\"\"&gt;${noticeEndTime}&lt;/span&gt; &lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;（北京时间，下同），登录&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;&lt;/span&gt;&lt;/span&gt;&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;（电子招标投标交易平台名称）下载电子招标文件。&lt;/span&gt;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-6f2b1efd=\"\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;&lt;strong data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp;&amp;nbsp;&lt;/strong&gt;4.2&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt; 招标文件每套售价&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;200&lt;/span&gt; 元&lt;/span&gt;&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;，售后不退。技术资料押金&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;200&lt;/span&gt; 元&lt;/span&gt;&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;，&lt;/span&gt;&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;在退还技术资料时退还（不计利息）。&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;/div&gt; &lt;h3 data-v-6f2b1efd=\"\" class=\"\\&amp;quot;tit\\&amp;quot;\"&gt;5. 投标文件的递交&lt;/h3&gt; &lt;div data-v-6f2b1efd=\"\" class=\"\\&amp;quot;context\\&amp;quot;\"&gt;&lt;p data-v-6f2b1efd=\"\"&gt;&lt;strong data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &lt;/strong&gt;&amp;nbsp; &lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;5.1 投标文件递交的截止时间（投标截止时间，下同）为&amp;nbsp;&lt;span data-v-6f2b1efd=\"\"&gt;${noticeEndTime}&lt;/span&gt; ，&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;投标人应在截止时间前通过&lt;/span&gt;&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;阳光招采平台（http://www.jy.jiezhaowang.com）&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;（电子招标投标交易平台）递交电子投标文件。&lt;/span&gt;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-6f2b1efd=\"\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;&lt;strong data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp; &lt;/strong&gt;5.2&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" style=\"text-indent: 32px;\"&gt;逾期送达的投标文件，电子招标投标交易平台将予以拒收。&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;/div&gt; &lt;h3 data-v-6f2b1efd=\"\" class=\"\\&amp;quot;tit\\&amp;quot;\"&gt;6. 发布公告的媒介&lt;/h3&gt; &lt;div data-v-6f2b1efd=\"\" class=\"\\&amp;quot;context\\&amp;quot;\"&gt;&lt;p data-v-6f2b1efd=\"\"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp; &lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;本次招标公告同时在&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;阳光招采平台&lt;/span&gt; （发布公告的媒介名称）上发布。&lt;/span&gt;&lt;/p&gt;&lt;/div&gt; &lt;h3 data-v-6f2b1efd=\"\" class=\"\\&amp;quot;tit\\&amp;quot;\"&gt;7. 联系方式&lt;/h3&gt; &lt;div data-v-6f2b1efd=\"\" class=\"\\&amp;quot;context\\&amp;quot;\"&gt;&lt;table data-v-6f2b1efd=\"\" cellpadding=\"5px\" style=\"border-collapse: collapse; width: 79.349%; height: 564px;\"&gt;&lt;tbody data-v-6f2b1efd=\"\"&gt;&lt;tr data-v-6f2b1efd=\"\" style=\"height: 58.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 58.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;招标人：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 58.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-family: &amp;quot;Microsoft YaHei&amp;quot;; text-align: right;\"&gt;招标代理机构：&amp;nbsp;&lt;/span&gt;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-family: &amp;quot;Microsoft YaHei&amp;quot;; text-align: right;\"&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 61.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 61.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;地址：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 61.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;地 址：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 46.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 46.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;邮编：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 46.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;邮编：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 54.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 54.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;联系人：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 54.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;联系人：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 50.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 50.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;电话：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;13000000001&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 50.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;电话：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;13000000002&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 63.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 63.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;传真：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 63.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;传真：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 55.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 55.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;电子邮件：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 55.4px;\"&gt;&lt;div data-v-6f2b1efd=\"\" class=\"\\&amp;quot;context\\&amp;quot;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;电子邮件：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/div&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 59.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 59.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;网址：&amp;nbsp;&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 59.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;网址：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 50.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 50.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;开户银行：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 50.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;开户银行：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&amp;nbsp;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt; &lt;tr data-v-6f2b1efd=\"\" style=\"height: 64.4px;\"&gt;&lt;td data-v-6f2b1efd=\"\" style=\"width: 49.6412%; height: 64.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;帐号：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt;&amp;nbsp;&amp;nbsp;&lt;/span&gt;&lt;/td&gt; &lt;td data-v-6f2b1efd=\"\" style=\"width: 50.3371%; height: 64.4px;\"&gt;&lt;span data-v-6f2b1efd=\"\" style=\"font-size: 16px;\"&gt;帐号：&lt;span data-v-6f2b1efd=\"\" class=\"textUnderline\"&gt;/&lt;/span&gt; &amp;nbsp;&amp;nbsp;&lt;/span&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;/div&gt;","noticeSendTime":"","noticeEndTime":"","publishType":1,"sectionType":2,"tenderProCode":"${purchaseProjectCode}","sectionList":[{"tpCode":"${purchaseProjectCode}","tpName":"${purchaseProjectName}","bidSectionCode":"${bidSectionCode1}","bidSectionName":"bidSectionName1","id":"${sectionId1}","ifUpload":1}],"tenderProId":"${tpId}","tenderProType":"2","tradeCenterName":"测试交易中心","tradeCenterCode":"001","regionCode":"130102","regionName":"河北省-石家庄市-长安区","bidMode":1,"tenderLxr":"河北顺恒集采中心有限公司","hostId":"1814243161552375808","hostName":"张聚平","hostOrgId":"10000-000257","hostTelephone":"16603190316","templateDetailId":"1892467458771746817","bulletinNature":0}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>etbtrade-tender/tenderBulletin/page?current=1&amp;size=10&amp;total=0&amp;sectionType=2&amp;bulletinType=4&amp;tenderProId=${tpId}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1781,29 +1603,11 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11.3"/>
-      <color rgb="FF0033B3"/>
-      <name val="JetBrains Mono"/>
-    </font>
-    <font>
-      <sz val="11.3"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="JetBrains Mono"/>
-    </font>
-    <font>
-      <sz val="11.3"/>
-      <color rgb="FF871094"/>
-      <name val="JetBrains Mono"/>
-    </font>
-    <font>
-      <sz val="11.3"/>
-      <color rgb="FF067D17"/>
-      <name val="JetBrains Mono"/>
-    </font>
-    <font>
-      <sz val="11.3"/>
-      <color rgb="FF080808"/>
-      <name val="JetBrains Mono"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1853,41 +1657,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2550,25 +2363,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="16.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="45" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="11.83203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="76.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
+    <col min="7" max="8" width="11.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
     <col min="10" max="10" width="53" style="3" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="3" customWidth="1"/>
     <col min="12" max="12" width="35" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="3" customWidth="1"/>
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2612,7 +2425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2620,7 +2433,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>17</v>
@@ -2632,27 +2445,27 @@
         <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>491</v>
+        <v>436</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>17</v>
@@ -2664,10 +2477,7 @@
         <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>25</v>
@@ -2676,15 +2486,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="B4" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>17</v>
@@ -2696,24 +2509,27 @@
         <v>39</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="B5" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>17</v>
@@ -2725,87 +2541,93 @@
         <v>39</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>413</v>
+        <v>467</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="6" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>459</v>
+      </c>
       <c r="B6" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>483</v>
+      <c r="D6" s="10" t="s">
+        <v>440</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="F6" s="10"/>
       <c r="G6" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>404</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="409.6">
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>402</v>
+      <c r="D7" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="10"/>
       <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>39</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+        <v>394</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="M7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>409</v>
+      <c r="D8" s="14" t="s">
+        <v>442</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>17</v>
@@ -2817,7 +2639,7 @@
         <v>39</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>405</v>
@@ -2826,148 +2648,174 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="B9" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>431</v>
+        <v>402</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>400</v>
+        <v>454</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="B10" s="1" t="s">
-        <v>416</v>
+        <v>401</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>395</v>
+        <v>31</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="B11" s="1" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>418</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>403</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>406</v>
+      <c r="J11" s="16" t="s">
+        <v>470</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="B12" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>395</v>
+        <v>444</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>407</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>420</v>
+        <v>40</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+        <v>408</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="165" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="B13" s="1" t="s">
-        <v>493</v>
+        <v>406</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>31</v>
+        <v>447</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>409</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+        <v>40</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="B14" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>395</v>
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>411</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>17</v>
@@ -2978,112 +2826,122 @@
       <c r="H14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+      <c r="J14" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" ht="165" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="B15" s="1" t="s">
-        <v>495</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>475</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>406</v>
-      </c>
+      <c r="J15" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="K15" s="12"/>
       <c r="M15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="B16" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>395</v>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>476</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>426</v>
+        <v>39</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>477</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+        <v>25</v>
+      </c>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>423</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>412</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>406</v>
+      <c r="J17" s="16" t="s">
+        <v>472</v>
       </c>
       <c r="M17" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="18" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>429</v>
+      <c r="D18" s="14" t="s">
+        <v>448</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>17</v>
@@ -3094,158 +2952,154 @@
       <c r="H18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>438</v>
+      <c r="J18" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>449</v>
       </c>
       <c r="M18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N18" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="90">
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>435</v>
+      <c r="D19" s="14" t="s">
+        <v>450</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>460</v>
+        <v>451</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" ht="180">
+    <row r="20" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>437</v>
+      <c r="D20" s="14" t="s">
+        <v>413</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>459</v>
+        <v>452</v>
+      </c>
+      <c r="K20" s="12"/>
+      <c r="M20" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" ht="409.6">
+    <row r="21" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>43</v>
+        <v>417</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="N21" s="1"/>
-    </row>
-    <row r="22" spans="1:14" ht="144">
+        <v>394</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>418</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="K22" s="12"/>
+        <v>40</v>
+      </c>
       <c r="M22" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N22" s="1"/>
-    </row>
-    <row r="23" spans="1:14" ht="409.6">
+    </row>
+    <row r="23" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>460</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>426</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>17</v>
@@ -3257,22 +3111,27 @@
         <v>19</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>444</v>
+        <v>40</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="M23" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="90">
-      <c r="A24" s="1"/>
+    <row r="24" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="B24" s="1" t="s">
-        <v>468</v>
+        <v>424</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="14" t="s">
-        <v>454</v>
+      <c r="D24" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>17</v>
@@ -3283,181 +3142,190 @@
       <c r="H24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="K24" s="12"/>
+      <c r="J24" s="16" t="s">
+        <v>479</v>
+      </c>
       <c r="M24" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N24" s="1"/>
-    </row>
-    <row r="25" spans="1:14" ht="90">
-      <c r="A25" s="1"/>
+      <c r="N24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="B25" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>467</v>
+        <v>457</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>480</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>475</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="L25" s="1"/>
       <c r="M25" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N25" s="1"/>
-    </row>
-    <row r="26" spans="1:14" ht="90">
-      <c r="A26" s="1"/>
+    </row>
+    <row r="26" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>461</v>
+      </c>
       <c r="B26" s="1" t="s">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>471</v>
+        <v>456</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="K26" s="12"/>
+        <v>430</v>
+      </c>
       <c r="M26" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N26" s="1"/>
-    </row>
-    <row r="27" spans="1:14" ht="409.6">
+      <c r="N26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>432</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>19</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>51</v>
+        <v>434</v>
       </c>
       <c r="M27" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="90">
+    <row r="28" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>448</v>
+        <v>38</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N28" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="90">
-      <c r="A29" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>462</v>
+      </c>
       <c r="B29" s="1" t="s">
-        <v>455</v>
+        <v>60</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="14" t="s">
-        <v>457</v>
+      <c r="D29" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>456</v>
+        <v>27</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="90">
+        <v>40</v>
+      </c>
+      <c r="K29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>54</v>
+        <v>463</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>451</v>
+        <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>449</v>
+        <v>65</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>18</v>
@@ -3465,11 +3333,8 @@
       <c r="H30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J30" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>466</v>
+      <c r="J30" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="M30" s="8" t="s">
         <v>25</v>
@@ -3478,21 +3343,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="90">
+    <row r="31" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>57</v>
+        <v>464</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>462</v>
+        <v>67</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>463</v>
+        <v>68</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>27</v>
@@ -3501,57 +3366,62 @@
         <v>39</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>400</v>
+        <v>69</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="M31" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N31" s="3">
+    </row>
+    <row r="32" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N32" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="90">
-      <c r="A32" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="90">
-      <c r="A33" s="1"/>
+    <row r="33" spans="1:13" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>466</v>
+      </c>
       <c r="B33" s="1" t="s">
-        <v>478</v>
+        <v>75</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>479</v>
+        <v>76</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>18</v>
@@ -3559,306 +3429,16 @@
       <c r="H33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>480</v>
+      <c r="J33" s="12" t="s">
+        <v>77</v>
       </c>
       <c r="M33" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="360">
-      <c r="A34" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N34" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="90">
-      <c r="A35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N35" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="90">
-      <c r="A36" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="90">
-      <c r="A37" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K37" s="1"/>
-      <c r="M37" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="90">
-      <c r="A38" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K38" s="1"/>
-      <c r="M38" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N38" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="409.6">
-      <c r="A39" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N39" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="90">
-      <c r="A40" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="M40" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="90">
-      <c r="A42" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="M42" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E42">
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="E2:E33">
     <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
@@ -3876,48 +3456,48 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA41 SW41 ACS41 AMO41 AWK41 BGG41 BQC41 BZY41 CJU41 CTQ41 DDM41 DNI41 DXE41 EHA41 EQW41 FAS41 FKO41 FUK41 GEG41 GOC41 GXY41 HHU41 HRQ41 IBM41 ILI41 IVE41 JFA41 JOW41 JYS41 KIO41 KSK41 LCG41 LMC41 LVY41 MFU41 MPQ41 MZM41 NJI41 NTE41 ODA41 OMW41 OWS41 PGO41 PQK41 QAG41 QKC41 QTY41 RDU41 RNQ41 RXM41 SHI41 SRE41 TBA41 TKW41 TUS41 UEO41 UOK41 UYG41 VIC41 VRY41 WBU41 WLQ41 WVM41 JA1:JA18 WVM1:WVM18 WLQ1:WLQ18 WBU1:WBU18 VRY1:VRY18 VIC1:VIC18 UYG1:UYG18 UOK1:UOK18 UEO1:UEO18 TUS1:TUS18 TKW1:TKW18 TBA1:TBA18 SRE1:SRE18 SHI1:SHI18 RXM1:RXM18 RNQ1:RNQ18 RDU1:RDU18 QTY1:QTY18 QKC1:QKC18 QAG1:QAG18 PQK1:PQK18 PGO1:PGO18 OWS1:OWS18 OMW1:OMW18 ODA1:ODA18 NTE1:NTE18 NJI1:NJI18 MZM1:MZM18 MPQ1:MPQ18 MFU1:MFU18 LVY1:LVY18 LMC1:LMC18 LCG1:LCG18 KSK1:KSK18 KIO1:KIO18 JYS1:JYS18 JOW1:JOW18 JFA1:JFA18 IVE1:IVE18 ILI1:ILI18 IBM1:IBM18 HRQ1:HRQ18 HHU1:HHU18 GXY1:GXY18 GOC1:GOC18 GEG1:GEG18 FUK1:FUK18 FKO1:FKO18 FAS1:FAS18 EQW1:EQW18 EHA1:EHA18 DXE1:DXE18 DNI1:DNI18 DDM1:DDM18 CTQ1:CTQ18 CJU1:CJU18 BZY1:BZY18 BQC1:BQC18 BGG1:BGG18 AWK1:AWK18 AMO1:AMO18 ACS1:ACS18 SW1:SW18" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA32 SW32 ACS32 AMO32 AWK32 BGG32 BQC32 BZY32 CJU32 CTQ32 DDM32 DNI32 DXE32 EHA32 EQW32 FAS32 FKO32 FUK32 GEG32 GOC32 GXY32 HHU32 HRQ32 IBM32 ILI32 IVE32 JFA32 JOW32 JYS32 KIO32 KSK32 LCG32 LMC32 LVY32 MFU32 MPQ32 MZM32 NJI32 NTE32 ODA32 OMW32 OWS32 PGO32 PQK32 QAG32 QKC32 QTY32 RDU32 RNQ32 RXM32 SHI32 SRE32 TBA32 TKW32 TUS32 UEO32 UOK32 UYG32 VIC32 VRY32 WBU32 WLQ32 WVM32 SW1:SW11 ACS1:ACS11 AMO1:AMO11 AWK1:AWK11 BGG1:BGG11 BQC1:BQC11 BZY1:BZY11 CJU1:CJU11 CTQ1:CTQ11 DDM1:DDM11 DNI1:DNI11 DXE1:DXE11 EHA1:EHA11 EQW1:EQW11 FAS1:FAS11 FKO1:FKO11 FUK1:FUK11 GEG1:GEG11 GOC1:GOC11 GXY1:GXY11 HHU1:HHU11 HRQ1:HRQ11 IBM1:IBM11 ILI1:ILI11 IVE1:IVE11 JFA1:JFA11 JOW1:JOW11 JYS1:JYS11 KIO1:KIO11 KSK1:KSK11 LCG1:LCG11 LMC1:LMC11 LVY1:LVY11 MFU1:MFU11 MPQ1:MPQ11 MZM1:MZM11 NJI1:NJI11 NTE1:NTE11 ODA1:ODA11 OMW1:OMW11 OWS1:OWS11 PGO1:PGO11 PQK1:PQK11 QAG1:QAG11 QKC1:QKC11 QTY1:QTY11 RDU1:RDU11 RNQ1:RNQ11 RXM1:RXM11 SHI1:SHI11 SRE1:SRE11 TBA1:TBA11 TKW1:TKW11 TUS1:TUS11 UEO1:UEO11 UOK1:UOK11 UYG1:UYG11 VIC1:VIC11 VRY1:VRY11 WBU1:WBU11 WLQ1:WLQ11 WVM1:WVM11 JA1:JA11" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JB41 SX41 ACT41 AMP41 AWL41 BGH41 BQD41 BZZ41 CJV41 CTR41 DDN41 DNJ41 DXF41 EHB41 EQX41 FAT41 FKP41 FUL41 GEH41 GOD41 GXZ41 HHV41 HRR41 IBN41 ILJ41 IVF41 JFB41 JOX41 JYT41 KIP41 KSL41 LCH41 LMD41 LVZ41 MFV41 MPR41 MZN41 NJJ41 NTF41 ODB41 OMX41 OWT41 PGP41 PQL41 QAH41 QKD41 QTZ41 RDV41 RNR41 RXN41 SHJ41 SRF41 TBB41 TKX41 TUT41 UEP41 UOL41 UYH41 VID41 VRZ41 WBV41 WLR41 WVN41 G1:G42 WVN1:WVN18 WLR1:WLR18 WBV1:WBV18 VRZ1:VRZ18 VID1:VID18 UYH1:UYH18 UOL1:UOL18 UEP1:UEP18 TUT1:TUT18 TKX1:TKX18 TBB1:TBB18 SRF1:SRF18 SHJ1:SHJ18 RXN1:RXN18 RNR1:RNR18 RDV1:RDV18 QTZ1:QTZ18 QKD1:QKD18 QAH1:QAH18 PQL1:PQL18 PGP1:PGP18 OWT1:OWT18 OMX1:OMX18 ODB1:ODB18 NTF1:NTF18 NJJ1:NJJ18 MZN1:MZN18 MPR1:MPR18 MFV1:MFV18 LVZ1:LVZ18 LMD1:LMD18 LCH1:LCH18 KSL1:KSL18 KIP1:KIP18 JYT1:JYT18 JOX1:JOX18 JFB1:JFB18 IVF1:IVF18 ILJ1:ILJ18 IBN1:IBN18 HRR1:HRR18 HHV1:HHV18 GXZ1:GXZ18 GOD1:GOD18 GEH1:GEH18 FUL1:FUL18 FKP1:FKP18 FAT1:FAT18 EQX1:EQX18 EHB1:EHB18 DXF1:DXF18 DNJ1:DNJ18 DDN1:DDN18 CTR1:CTR18 CJV1:CJV18 BZZ1:BZZ18 BQD1:BQD18 BGH1:BGH18 AWL1:AWL18 AMP1:AMP18 ACT1:ACT18 SX1:SX18 JB1:JB18" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JB32 SX32 ACT32 AMP32 AWL32 BGH32 BQD32 BZZ32 CJV32 CTR32 DDN32 DNJ32 DXF32 EHB32 EQX32 FAT32 FKP32 FUL32 GEH32 GOD32 GXZ32 HHV32 HRR32 IBN32 ILJ32 IVF32 JFB32 JOX32 JYT32 KIP32 KSL32 LCH32 LMD32 LVZ32 MFV32 MPR32 MZN32 NJJ32 NTF32 ODB32 OMX32 OWT32 PGP32 PQL32 QAH32 QKD32 QTZ32 RDV32 RNR32 RXN32 SHJ32 SRF32 TBB32 TKX32 TUT32 UEP32 UOL32 UYH32 VID32 VRZ32 WBV32 WLR32 WVN32 JB1:JB11 SX1:SX11 ACT1:ACT11 AMP1:AMP11 AWL1:AWL11 BGH1:BGH11 BQD1:BQD11 BZZ1:BZZ11 CJV1:CJV11 CTR1:CTR11 DDN1:DDN11 DNJ1:DNJ11 DXF1:DXF11 EHB1:EHB11 EQX1:EQX11 FAT1:FAT11 FKP1:FKP11 FUL1:FUL11 GEH1:GEH11 GOD1:GOD11 GXZ1:GXZ11 HHV1:HHV11 HRR1:HRR11 IBN1:IBN11 ILJ1:ILJ11 IVF1:IVF11 JFB1:JFB11 JOX1:JOX11 JYT1:JYT11 KIP1:KIP11 KSL1:KSL11 LCH1:LCH11 LMD1:LMD11 LVZ1:LVZ11 MFV1:MFV11 MPR1:MPR11 MZN1:MZN11 NJJ1:NJJ11 NTF1:NTF11 ODB1:ODB11 OMX1:OMX11 OWT1:OWT11 PGP1:PGP11 PQL1:PQL11 QAH1:QAH11 QKD1:QKD11 QTZ1:QTZ11 RDV1:RDV11 RNR1:RNR11 RXN1:RXN11 SHJ1:SHJ11 SRF1:SRF11 TBB1:TBB11 TKX1:TKX11 TUT1:TUT11 UEP1:UEP11 UOL1:UOL11 UYH1:UYH11 VID1:VID11 VRZ1:VRZ11 WBV1:WBV11 WLR1:WLR11 WVN1:WVN11 G1:G33" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"get,post,put,delete,head,options,patch"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JC41 SY41 ACU41 AMQ41 AWM41 BGI41 BQE41 CAA41 CJW41 CTS41 DDO41 DNK41 DXG41 EHC41 EQY41 FAU41 FKQ41 FUM41 GEI41 GOE41 GYA41 HHW41 HRS41 IBO41 ILK41 IVG41 JFC41 JOY41 JYU41 KIQ41 KSM41 LCI41 LME41 LWA41 MFW41 MPS41 MZO41 NJK41 NTG41 ODC41 OMY41 OWU41 PGQ41 PQM41 QAI41 QKE41 QUA41 RDW41 RNS41 RXO41 SHK41 SRG41 TBC41 TKY41 TUU41 UEQ41 UOM41 UYI41 VIE41 VSA41 WBW41 WLS41 WVO41 H1:H42 WVO1:WVO18 WLS1:WLS18 WBW1:WBW18 VSA1:VSA18 VIE1:VIE18 UYI1:UYI18 UOM1:UOM18 UEQ1:UEQ18 TUU1:TUU18 TKY1:TKY18 TBC1:TBC18 SRG1:SRG18 SHK1:SHK18 RXO1:RXO18 RNS1:RNS18 RDW1:RDW18 QUA1:QUA18 QKE1:QKE18 QAI1:QAI18 PQM1:PQM18 PGQ1:PGQ18 OWU1:OWU18 OMY1:OMY18 ODC1:ODC18 NTG1:NTG18 NJK1:NJK18 MZO1:MZO18 MPS1:MPS18 MFW1:MFW18 LWA1:LWA18 LME1:LME18 LCI1:LCI18 KSM1:KSM18 KIQ1:KIQ18 JYU1:JYU18 JOY1:JOY18 JFC1:JFC18 IVG1:IVG18 ILK1:ILK18 IBO1:IBO18 HRS1:HRS18 HHW1:HHW18 GYA1:GYA18 GOE1:GOE18 GEI1:GEI18 FUM1:FUM18 FKQ1:FKQ18 FAU1:FAU18 EQY1:EQY18 EHC1:EHC18 DXG1:DXG18 DNK1:DNK18 DDO1:DDO18 CTS1:CTS18 CJW1:CJW18 CAA1:CAA18 BQE1:BQE18 BGI1:BGI18 AWM1:AWM18 AMQ1:AMQ18 ACU1:ACU18 SY1:SY18 JC1:JC18" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JC32 SY32 ACU32 AMQ32 AWM32 BGI32 BQE32 CAA32 CJW32 CTS32 DDO32 DNK32 DXG32 EHC32 EQY32 FAU32 FKQ32 FUM32 GEI32 GOE32 GYA32 HHW32 HRS32 IBO32 ILK32 IVG32 JFC32 JOY32 JYU32 KIQ32 KSM32 LCI32 LME32 LWA32 MFW32 MPS32 MZO32 NJK32 NTG32 ODC32 OMY32 OWU32 PGQ32 PQM32 QAI32 QKE32 QUA32 RDW32 RNS32 RXO32 SHK32 SRG32 TBC32 TKY32 TUU32 UEQ32 UOM32 UYI32 VIE32 VSA32 WBW32 WLS32 WVO32 JC1:JC11 SY1:SY11 ACU1:ACU11 AMQ1:AMQ11 AWM1:AWM11 BGI1:BGI11 BQE1:BQE11 CAA1:CAA11 CJW1:CJW11 CTS1:CTS11 DDO1:DDO11 DNK1:DNK11 DXG1:DXG11 EHC1:EHC11 EQY1:EQY11 FAU1:FAU11 FKQ1:FKQ11 FUM1:FUM11 GEI1:GEI11 GOE1:GOE11 GYA1:GYA11 HHW1:HHW11 HRS1:HRS11 IBO1:IBO11 ILK1:ILK11 IVG1:IVG11 JFC1:JFC11 JOY1:JOY11 JYU1:JYU11 KIQ1:KIQ11 KSM1:KSM11 LCI1:LCI11 LME1:LME11 LWA1:LWA11 MFW1:MFW11 MPS1:MPS11 MZO1:MZO11 NJK1:NJK11 NTG1:NTG11 ODC1:ODC11 OMY1:OMY11 OWU1:OWU11 PGQ1:PGQ11 PQM1:PQM11 QAI1:QAI11 QKE1:QKE11 QUA1:QUA11 RDW1:RDW11 RNS1:RNS11 RXO1:RXO11 SHK1:SHK11 SRG1:SRG11 TBC1:TBC11 TKY1:TKY11 TUU1:TUU11 UEQ1:UEQ11 UOM1:UOM11 UYI1:UYI11 VIE1:VIE11 VSA1:VSA11 WBW1:WBW11 WLS1:WLS11 WVO1:WVO11 H1:H33" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"params,data,json"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E42" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E33" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"P1,P2,P3,P4,P5"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D34" r:id="rId1" display="http://trade.qy-test.zszc.jianshicha.cn/etbApi/etbtrade/tenderFile/${tfid}" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D24" r:id="rId1" display="http://trade.qy-test.zszc.jianshicha.cn/etbApi/etbtrade/tenderFile/${tfid}" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="16.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="3" customWidth="1"/>
     <col min="4" max="4" width="45" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="11.83203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
+    <col min="7" max="8" width="11.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="3" customWidth="1"/>
     <col min="12" max="12" width="35" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="3" customWidth="1"/>
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3961,12 +3541,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>16</v>
@@ -3981,27 +3561,27 @@
         <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="90">
+    <row r="3" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>34</v>
@@ -4015,7 +3595,7 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -4024,18 +3604,18 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="126">
+    <row r="4" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>34</v>
@@ -4047,7 +3627,7 @@
         <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K4" s="1"/>
       <c r="M4" s="1" t="s">
@@ -4055,18 +3635,18 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="90">
+    <row r="5" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>34</v>
@@ -4086,18 +3666,18 @@
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="90">
+    <row r="6" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>34</v>
@@ -4110,24 +3690,24 @@
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="90">
+    <row r="7" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>34</v>
@@ -4139,27 +3719,27 @@
         <v>19</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="90">
-      <c r="A8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>34</v>
@@ -4175,18 +3755,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="409.6">
+    <row r="9" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>34</v>
@@ -4198,27 +3778,27 @@
         <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="90">
-      <c r="A10" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>34</v>
@@ -4230,24 +3810,24 @@
         <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="90">
+    <row r="11" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>34</v>
@@ -4259,15 +3839,47 @@
         <v>19</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E11">
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
@@ -4285,16 +3897,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G11 JB1:JB2 SX1:SX2 ACT1:ACT2 AMP1:AMP2 AWL1:AWL2 BGH1:BGH2 BQD1:BQD2 BZZ1:BZZ2 CJV1:CJV2 CTR1:CTR2 DDN1:DDN2 DNJ1:DNJ2 DXF1:DXF2 EHB1:EHB2 EQX1:EQX2 FAT1:FAT2 FKP1:FKP2 FUL1:FUL2 GEH1:GEH2 GOD1:GOD2 GXZ1:GXZ2 HHV1:HHV2 HRR1:HRR2 IBN1:IBN2 ILJ1:ILJ2 IVF1:IVF2 JFB1:JFB2 JOX1:JOX2 JYT1:JYT2 KIP1:KIP2 KSL1:KSL2 LCH1:LCH2 LMD1:LMD2 LVZ1:LVZ2 MFV1:MFV2 MPR1:MPR2 MZN1:MZN2 NJJ1:NJJ2 NTF1:NTF2 ODB1:ODB2 OMX1:OMX2 OWT1:OWT2 PGP1:PGP2 PQL1:PQL2 QAH1:QAH2 QKD1:QKD2 QTZ1:QTZ2 RDV1:RDV2 RNR1:RNR2 RXN1:RXN2 SHJ1:SHJ2 SRF1:SRF2 TBB1:TBB2 TKX1:TKX2 TUT1:TUT2 UEP1:UEP2 UOL1:UOL2 UYH1:UYH2 VID1:VID2 VRZ1:VRZ2 WBV1:WBV2 WLR1:WLR2 WVN1:WVN2" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G12 JB1:JB2 SX1:SX2 ACT1:ACT2 AMP1:AMP2 AWL1:AWL2 BGH1:BGH2 BQD1:BQD2 BZZ1:BZZ2 CJV1:CJV2 CTR1:CTR2 DDN1:DDN2 DNJ1:DNJ2 DXF1:DXF2 EHB1:EHB2 EQX1:EQX2 FAT1:FAT2 FKP1:FKP2 FUL1:FUL2 GEH1:GEH2 GOD1:GOD2 GXZ1:GXZ2 HHV1:HHV2 HRR1:HRR2 IBN1:IBN2 ILJ1:ILJ2 IVF1:IVF2 JFB1:JFB2 JOX1:JOX2 JYT1:JYT2 KIP1:KIP2 KSL1:KSL2 LCH1:LCH2 LMD1:LMD2 LVZ1:LVZ2 MFV1:MFV2 MPR1:MPR2 MZN1:MZN2 NJJ1:NJJ2 NTF1:NTF2 ODB1:ODB2 OMX1:OMX2 OWT1:OWT2 PGP1:PGP2 PQL1:PQL2 QAH1:QAH2 QKD1:QKD2 QTZ1:QTZ2 RDV1:RDV2 RNR1:RNR2 RXN1:RXN2 SHJ1:SHJ2 SRF1:SRF2 TBB1:TBB2 TKX1:TKX2 TUT1:TUT2 UEP1:UEP2 UOL1:UOL2 UYH1:UYH2 VID1:VID2 VRZ1:VRZ2 WBV1:WBV2 WLR1:WLR2 WVN1:WVN2 JB12 SX12 ACT12 AMP12 AWL12 BGH12 BQD12 BZZ12 CJV12 CTR12 DDN12 DNJ12 DXF12 EHB12 EQX12 FAT12 FKP12 FUL12 GEH12 GOD12 GXZ12 HHV12 HRR12 IBN12 ILJ12 IVF12 JFB12 JOX12 JYT12 KIP12 KSL12 LCH12 LMD12 LVZ12 MFV12 MPR12 MZN12 NJJ12 NTF12 ODB12 OMX12 OWT12 PGP12 PQL12 QAH12 QKD12 QTZ12 RDV12 RNR12 RXN12 SHJ12 SRF12 TBB12 TKX12 TUT12 UEP12 UOL12 UYH12 VID12 VRZ12 WBV12 WLR12 WVN12" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"get,post,put,delete,head,options,patch"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E11" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E12" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"P1,P2,P3,P4,P5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H11 JC1:JC2 SY1:SY2 ACU1:ACU2 AMQ1:AMQ2 AWM1:AWM2 BGI1:BGI2 BQE1:BQE2 CAA1:CAA2 CJW1:CJW2 CTS1:CTS2 DDO1:DDO2 DNK1:DNK2 DXG1:DXG2 EHC1:EHC2 EQY1:EQY2 FAU1:FAU2 FKQ1:FKQ2 FUM1:FUM2 GEI1:GEI2 GOE1:GOE2 GYA1:GYA2 HHW1:HHW2 HRS1:HRS2 IBO1:IBO2 ILK1:ILK2 IVG1:IVG2 JFC1:JFC2 JOY1:JOY2 JYU1:JYU2 KIQ1:KIQ2 KSM1:KSM2 LCI1:LCI2 LME1:LME2 LWA1:LWA2 MFW1:MFW2 MPS1:MPS2 MZO1:MZO2 NJK1:NJK2 NTG1:NTG2 ODC1:ODC2 OMY1:OMY2 OWU1:OWU2 PGQ1:PGQ2 PQM1:PQM2 QAI1:QAI2 QKE1:QKE2 QUA1:QUA2 RDW1:RDW2 RNS1:RNS2 RXO1:RXO2 SHK1:SHK2 SRG1:SRG2 TBC1:TBC2 TKY1:TKY2 TUU1:TUU2 UEQ1:UEQ2 UOM1:UOM2 UYI1:UYI2 VIE1:VIE2 VSA1:VSA2 WBW1:WBW2 WLS1:WLS2 WVO1:WVO2" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H12 JC1:JC2 SY1:SY2 ACU1:ACU2 AMQ1:AMQ2 AWM1:AWM2 BGI1:BGI2 BQE1:BQE2 CAA1:CAA2 CJW1:CJW2 CTS1:CTS2 DDO1:DDO2 DNK1:DNK2 DXG1:DXG2 EHC1:EHC2 EQY1:EQY2 FAU1:FAU2 FKQ1:FKQ2 FUM1:FUM2 GEI1:GEI2 GOE1:GOE2 GYA1:GYA2 HHW1:HHW2 HRS1:HRS2 IBO1:IBO2 ILK1:ILK2 IVG1:IVG2 JFC1:JFC2 JOY1:JOY2 JYU1:JYU2 KIQ1:KIQ2 KSM1:KSM2 LCI1:LCI2 LME1:LME2 LWA1:LWA2 MFW1:MFW2 MPS1:MPS2 MZO1:MZO2 NJK1:NJK2 NTG1:NTG2 ODC1:ODC2 OMY1:OMY2 OWU1:OWU2 PGQ1:PGQ2 PQM1:PQM2 QAI1:QAI2 QKE1:QKE2 QUA1:QUA2 RDW1:RDW2 RNS1:RNS2 RXO1:RXO2 SHK1:SHK2 SRG1:SRG2 TBC1:TBC2 TKY1:TKY2 TUU1:TUU2 UEQ1:UEQ2 UOM1:UOM2 UYI1:UYI2 VIE1:VIE2 VSA1:VSA2 WBW1:WBW2 WLS1:WLS2 WVO1:WVO2 JC12 SY12 ACU12 AMQ12 AWM12 BGI12 BQE12 CAA12 CJW12 CTS12 DDO12 DNK12 DXG12 EHC12 EQY12 FAU12 FKQ12 FUM12 GEI12 GOE12 GYA12 HHW12 HRS12 IBO12 ILK12 IVG12 JFC12 JOY12 JYU12 KIQ12 KSM12 LCI12 LME12 LWA12 MFW12 MPS12 MZO12 NJK12 NTG12 ODC12 OMY12 OWU12 PGQ12 PQM12 QAI12 QKE12 QUA12 RDW12 RNS12 RXO12 SHK12 SRG12 TBC12 TKY12 TUU12 UEQ12 UOM12 UYI12 VIE12 VSA12 WBW12 WLS12 WVO12" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"params,data,json"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA1:JA2 SW1:SW2 ACS1:ACS2 AMO1:AMO2 AWK1:AWK2 BGG1:BGG2 BQC1:BQC2 BZY1:BZY2 CJU1:CJU2 CTQ1:CTQ2 DDM1:DDM2 DNI1:DNI2 DXE1:DXE2 EHA1:EHA2 EQW1:EQW2 FAS1:FAS2 FKO1:FKO2 FUK1:FUK2 GEG1:GEG2 GOC1:GOC2 GXY1:GXY2 HHU1:HHU2 HRQ1:HRQ2 IBM1:IBM2 ILI1:ILI2 IVE1:IVE2 JFA1:JFA2 JOW1:JOW2 JYS1:JYS2 KIO1:KIO2 KSK1:KSK2 LCG1:LCG2 LMC1:LMC2 LVY1:LVY2 MFU1:MFU2 MPQ1:MPQ2 MZM1:MZM2 NJI1:NJI2 NTE1:NTE2 ODA1:ODA2 OMW1:OMW2 OWS1:OWS2 PGO1:PGO2 PQK1:PQK2 QAG1:QAG2 QKC1:QKC2 QTY1:QTY2 RDU1:RDU2 RNQ1:RNQ2 RXM1:RXM2 SHI1:SHI2 SRE1:SRE2 TBA1:TBA2 TKW1:TKW2 TUS1:TUS2 UEO1:UEO2 UOK1:UOK2 UYG1:UYG2 VIC1:VIC2 VRY1:VRY2 WBU1:WBU2 WLQ1:WLQ2 WVM1:WVM2" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA1:JA2 SW1:SW2 ACS1:ACS2 AMO1:AMO2 AWK1:AWK2 BGG1:BGG2 BQC1:BQC2 BZY1:BZY2 CJU1:CJU2 CTQ1:CTQ2 DDM1:DDM2 DNI1:DNI2 DXE1:DXE2 EHA1:EHA2 EQW1:EQW2 FAS1:FAS2 FKO1:FKO2 FUK1:FUK2 GEG1:GEG2 GOC1:GOC2 GXY1:GXY2 HHU1:HHU2 HRQ1:HRQ2 IBM1:IBM2 ILI1:ILI2 IVE1:IVE2 JFA1:JFA2 JOW1:JOW2 JYS1:JYS2 KIO1:KIO2 KSK1:KSK2 LCG1:LCG2 LMC1:LMC2 LVY1:LVY2 MFU1:MFU2 MPQ1:MPQ2 MZM1:MZM2 NJI1:NJI2 NTE1:NTE2 ODA1:ODA2 OMW1:OMW2 OWS1:OWS2 PGO1:PGO2 PQK1:PQK2 QAG1:QAG2 QKC1:QKC2 QTY1:QTY2 RDU1:RDU2 RNQ1:RNQ2 RXM1:RXM2 SHI1:SHI2 SRE1:SRE2 TBA1:TBA2 TKW1:TKW2 TUS1:TUS2 UEO1:UEO2 UOK1:UOK2 UYG1:UYG2 VIC1:VIC2 VRY1:VRY2 WBU1:WBU2 WLQ1:WLQ2 WVM1:WVM2 SW12 ACS12 AMO12 AWK12 BGG12 BQC12 BZY12 CJU12 CTQ12 DDM12 DNI12 DXE12 EHA12 EQW12 FAS12 FKO12 FUK12 GEG12 GOC12 GXY12 HHU12 HRQ12 IBM12 ILI12 IVE12 JFA12 JOW12 JYS12 KIO12 KSK12 LCG12 LMC12 LVY12 MFU12 MPQ12 MZM12 NJI12 NTE12 ODA12 OMW12 OWS12 PGO12 PQK12 QAG12 QKC12 QTY12 RDU12 RNQ12 RXM12 SHI12 SRE12 TBA12 TKW12 TUS12 UEO12 UOK12 UYG12 VIC12 VRY12 WBU12 WLQ12 WVM12 JA12" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4306,24 +3918,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="16.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="3" customWidth="1"/>
     <col min="4" max="4" width="45" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="11.83203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
+    <col min="7" max="8" width="11.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="3" customWidth="1"/>
     <col min="12" max="12" width="35" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="3" customWidth="1"/>
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4367,12 +3979,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>16</v>
@@ -4387,27 +3999,27 @@
         <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="90">
+    <row r="3" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>34</v>
@@ -4421,7 +4033,7 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -4430,18 +4042,18 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="126">
+    <row r="4" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>34</v>
@@ -4453,7 +4065,7 @@
         <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K4" s="1"/>
       <c r="M4" s="1" t="s">
@@ -4461,18 +4073,18 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="90">
+    <row r="5" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>34</v>
@@ -4492,18 +4104,18 @@
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="90">
+    <row r="6" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>34</v>
@@ -4516,24 +4128,24 @@
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="90">
+    <row r="7" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>34</v>
@@ -4545,27 +4157,27 @@
         <v>19</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="90">
-      <c r="A8" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>34</v>
@@ -4581,18 +4193,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="409.6">
+    <row r="9" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>34</v>
@@ -4604,27 +4216,27 @@
         <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="90">
-      <c r="A10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>34</v>
@@ -4636,24 +4248,24 @@
         <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="90">
+    <row r="11" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>34</v>
@@ -4665,14 +4277,14 @@
         <v>19</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="E2:E11">
     <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"P5"</formula>
@@ -4712,24 +4324,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="16.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="3" customWidth="1"/>
     <col min="4" max="4" width="45" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="11.83203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
+    <col min="7" max="8" width="11.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="3" customWidth="1"/>
     <col min="12" max="12" width="35" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="3" customWidth="1"/>
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4773,12 +4385,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>16</v>
@@ -4793,27 +4405,27 @@
         <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="90">
+    <row r="3" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>34</v>
@@ -4827,7 +4439,7 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -4836,18 +4448,18 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="126">
+    <row r="4" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>34</v>
@@ -4859,7 +4471,7 @@
         <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K4" s="1"/>
       <c r="M4" s="1" t="s">
@@ -4867,18 +4479,18 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="90">
+    <row r="5" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>34</v>
@@ -4898,18 +4510,18 @@
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="90">
+    <row r="6" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>34</v>
@@ -4922,24 +4534,24 @@
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="90">
+    <row r="7" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>34</v>
@@ -4951,27 +4563,27 @@
         <v>19</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="90">
-      <c r="A8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>34</v>
@@ -4987,18 +4599,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="409.6">
+    <row r="9" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>34</v>
@@ -5010,27 +4622,27 @@
         <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="90">
-      <c r="A10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>34</v>
@@ -5042,24 +4654,24 @@
         <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="90">
+    <row r="11" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>34</v>
@@ -5071,14 +4683,14 @@
         <v>19</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="E2:E11">
     <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
       <formula>"P5"</formula>
@@ -5118,24 +4730,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="16.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="71.1640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="11.83203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="71.125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
+    <col min="7" max="8" width="11.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="3" customWidth="1"/>
     <col min="12" max="12" width="35" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="3" customWidth="1"/>
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -5179,18 +4791,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>18</v>
@@ -5199,149 +4811,149 @@
         <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="M3" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="E4" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E5" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="B5" s="1" t="s">
+      <c r="E6" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E7" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>18</v>
@@ -5350,27 +4962,27 @@
         <v>19</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="90">
+    <row r="8" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="1" t="s">
@@ -5390,21 +5002,21 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="90">
+    <row r="9" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="E9" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="1" t="s">
@@ -5423,21 +5035,21 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="1" t="s">
@@ -5452,24 +5064,24 @@
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="90">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="1" t="s">
@@ -5488,21 +5100,21 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" ht="90">
+    <row r="12" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="1" t="s">
@@ -5521,21 +5133,21 @@
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" ht="90">
+    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="1" t="s">
@@ -5554,21 +5166,21 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" ht="90">
+    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="1" t="s">
@@ -5587,21 +5199,21 @@
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" ht="90">
+    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="1" t="s">
@@ -5612,7 +5224,7 @@
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -5621,21 +5233,21 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="90">
+    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="1" t="s">
@@ -5654,21 +5266,21 @@
       </c>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1" t="s">
@@ -5686,21 +5298,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="1" t="s">
@@ -5718,21 +5330,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="1" t="s">
@@ -5750,21 +5362,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1" t="s">
@@ -5779,21 +5391,21 @@
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>18</v>
@@ -5802,30 +5414,30 @@
         <v>19</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M21" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="90">
+    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
@@ -5839,7 +5451,7 @@
         <v>40</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="8" t="s">
@@ -5847,21 +5459,21 @@
       </c>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>27</v>
@@ -5876,19 +5488,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="90">
+    <row r="24" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
@@ -5908,21 +5520,21 @@
       </c>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" ht="90">
+    <row r="25" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
@@ -5942,21 +5554,21 @@
       </c>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>18</v>
@@ -5965,27 +5577,27 @@
         <v>19</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M26" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="27" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="1" t="s">
@@ -6001,21 +5613,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="28" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="E28" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="1" t="s">
@@ -6032,21 +5644,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="29" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="1" t="s">
@@ -6061,24 +5673,24 @@
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="1" t="s">
@@ -6095,21 +5707,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="31" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="1" t="s">
@@ -6126,21 +5738,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="32" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="1" t="s">
@@ -6157,21 +5769,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="33" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="1" t="s">
@@ -6188,21 +5800,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="34" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="1" t="s">
@@ -6212,27 +5824,27 @@
         <v>19</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="35" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="1" t="s">
@@ -6249,21 +5861,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="36" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="1" t="s">
@@ -6281,21 +5893,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="37" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="1" t="s">
@@ -6313,21 +5925,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="38" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="1" t="s">
@@ -6345,21 +5957,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="39" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="1" t="s">
@@ -6374,21 +5986,21 @@
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>18</v>
@@ -6397,62 +6009,62 @@
         <v>19</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M40" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="41" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E41" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K41" s="1" t="s">
+      <c r="M41" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M41" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="90">
-      <c r="A42" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="E42" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1" t="s">
@@ -6472,18 +6084,18 @@
       </c>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="43" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>27</v>
@@ -6498,21 +6110,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="90">
+    <row r="44" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
@@ -6532,21 +6144,21 @@
       </c>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="45" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>18</v>
@@ -6555,27 +6167,27 @@
         <v>19</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M45" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="46" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="1" t="s">
@@ -6591,21 +6203,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="47" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="E47" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="1" t="s">
@@ -6622,21 +6234,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="48" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="1" t="s">
@@ -6651,24 +6263,24 @@
       </c>
       <c r="L48" s="3"/>
       <c r="M48" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="1" t="s">
@@ -6685,21 +6297,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="50" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="1" t="s">
@@ -6716,21 +6328,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="90">
+    <row r="51" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="1" t="s">
@@ -6748,21 +6360,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="90">
+    <row r="52" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="1" t="s">
@@ -6780,21 +6392,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="90">
+    <row r="53" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="1" t="s">
@@ -6805,7 +6417,7 @@
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -6813,21 +6425,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="90">
+    <row r="54" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="1" t="s">
@@ -6845,21 +6457,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="90">
+    <row r="55" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>27</v>
@@ -6875,21 +6487,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="90">
+    <row r="56" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>27</v>
@@ -6905,21 +6517,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="90">
+    <row r="57" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>27</v>
@@ -6935,21 +6547,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="90">
+    <row r="58" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>27</v>
@@ -6962,22 +6574,22 @@
       </c>
       <c r="K58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="54">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
@@ -6999,18 +6611,18 @@
       </c>
       <c r="N59" s="1"/>
     </row>
-    <row r="60" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="60" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>27</v>
@@ -7025,21 +6637,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="61" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F61" s="10"/>
       <c r="G61" s="1" t="s">
@@ -7055,21 +6667,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="62" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="1" t="s">
@@ -7084,24 +6696,24 @@
       </c>
       <c r="L62" s="3"/>
       <c r="M62" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F63" s="10"/>
       <c r="G63" s="1" t="s">
@@ -7118,21 +6730,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="64" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F64" s="10"/>
       <c r="G64" s="1" t="s">
@@ -7149,21 +6761,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="90">
+    <row r="65" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F65" s="10"/>
       <c r="G65" s="1" t="s">
@@ -7181,18 +6793,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="90">
+    <row r="66" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F66" s="10"/>
       <c r="G66" s="1" t="s">
@@ -7205,21 +6817,21 @@
         <v>40</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="90">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F67" s="10"/>
       <c r="G67" s="1" t="s">
@@ -7235,18 +6847,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="90">
+    <row r="68" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F68" s="10"/>
       <c r="G68" s="1" t="s">
@@ -7262,18 +6874,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="69" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>18</v>
@@ -7282,30 +6894,30 @@
         <v>19</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M69" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="90">
+    <row r="70" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>32</v>
@@ -7324,21 +6936,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="90">
+    <row r="71" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>32</v>
@@ -7351,27 +6963,27 @@
       </c>
       <c r="K71" s="1"/>
       <c r="M71" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N71" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="90">
+    <row r="72" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>27</v>
@@ -7390,21 +7002,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="90">
+    <row r="73" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>32</v>
@@ -7423,21 +7035,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="90">
+    <row r="74" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>27</v>
@@ -7450,24 +7062,24 @@
       </c>
       <c r="K74" s="1"/>
       <c r="M74" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N74" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="75" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>18</v>
@@ -7476,30 +7088,30 @@
         <v>19</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M75" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="90">
+    <row r="76" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>32</v>
@@ -7518,21 +7130,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="90">
+    <row r="77" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>32</v>
@@ -7545,27 +7157,27 @@
       </c>
       <c r="K77" s="1"/>
       <c r="M77" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N77" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="90">
+    <row r="78" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>27</v>
@@ -7584,21 +7196,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="90">
+    <row r="79" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>32</v>
@@ -7617,21 +7229,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="90">
+    <row r="80" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>27</v>
@@ -7644,24 +7256,24 @@
       </c>
       <c r="K80" s="1"/>
       <c r="M80" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N80" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="81" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>18</v>
@@ -7670,30 +7282,30 @@
         <v>19</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M81" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="90">
+    <row r="82" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>32</v>
@@ -7712,21 +7324,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="90">
+    <row r="83" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>32</v>
@@ -7739,27 +7351,27 @@
       </c>
       <c r="K83" s="1"/>
       <c r="M83" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N83" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="90">
+    <row r="84" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>27</v>
@@ -7778,21 +7390,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="90">
+    <row r="85" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>32</v>
@@ -7811,21 +7423,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="90">
+    <row r="86" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>27</v>
@@ -7838,25 +7450,25 @@
       </c>
       <c r="K86" s="1"/>
       <c r="M86" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N86" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="54">
+    <row r="87" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
@@ -7878,21 +7490,21 @@
       </c>
       <c r="N87" s="1"/>
     </row>
-    <row r="88" spans="1:14" ht="90">
+    <row r="88" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>27</v>
@@ -7911,21 +7523,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="90">
+    <row r="89" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>18</v>
@@ -7944,21 +7556,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="90">
+    <row r="90" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>18</v>
@@ -7977,21 +7589,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="90">
+    <row r="91" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>32</v>
@@ -8010,15 +7622,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="100" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E100" s="6"/>
       <c r="M100" s="8"/>
     </row>
-    <row r="101" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="101" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E101" s="6"/>
       <c r="M101" s="8"/>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -8030,7 +7642,7 @@
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -8042,7 +7654,7 @@
       <c r="M103" s="8"/>
       <c r="N103" s="1"/>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -8055,7 +7667,7 @@
       <c r="M104" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="E2:E91">
     <cfRule type="cellIs" dxfId="14" priority="31" operator="equal">
       <formula>"P5"</formula>
@@ -8130,24 +7742,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="16.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="3" customWidth="1"/>
     <col min="4" max="4" width="45" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.83203125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="11.83203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.875" style="3" customWidth="1"/>
+    <col min="7" max="8" width="11.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="3" customWidth="1"/>
     <col min="12" max="12" width="35" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="3" customWidth="1"/>
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -8191,18 +7803,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>18</v>
@@ -8220,21 +7832,21 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="409.6">
+    <row r="3" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
@@ -8245,7 +7857,7 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -8254,21 +7866,21 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="90">
+    <row r="4" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
@@ -8279,10 +7891,10 @@
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
@@ -8290,21 +7902,21 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="180">
+    <row r="5" spans="1:14" ht="165" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>27</v>
@@ -8316,26 +7928,26 @@
         <v>40</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="108">
+    <row r="6" spans="1:14" ht="99" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>18</v>
@@ -8344,31 +7956,31 @@
         <v>19</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" ht="90">
+    <row r="7" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>32</v>
@@ -8385,19 +7997,19 @@
       </c>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="90">
+    <row r="8" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>27</v>
@@ -8414,19 +8026,19 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="72">
+    <row r="9" spans="1:14" ht="66" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>18</v>
@@ -8435,62 +8047,62 @@
         <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="90">
+    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="M10" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="90">
-      <c r="A11" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E11" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>18</v>
@@ -8506,21 +8118,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="90">
+    <row r="12" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>27</v>
@@ -8536,128 +8148,128 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="90">
+    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="E14" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="90">
-      <c r="A14" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E15" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="90">
-      <c r="B15" s="1" t="s">
+      <c r="E16" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="90">
-      <c r="B16" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" ht="90">
-      <c r="B17" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E17" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>27</v>
@@ -8673,18 +8285,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="90">
+    <row r="18" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>27</v>
@@ -8699,21 +8311,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="90">
+    <row r="19" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>39</v>
@@ -8728,18 +8340,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="90">
+    <row r="20" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>18</v>
@@ -8754,16 +8366,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="72">
+    <row r="21" spans="2:14" ht="66" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>18</v>
@@ -8772,56 +8384,56 @@
         <v>19</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="M21" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="90">
+    <row r="22" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" ht="90">
-      <c r="B23" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E23" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>18</v>
@@ -8837,18 +8449,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="90">
+    <row r="24" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>27</v>
@@ -8864,122 +8476,122 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="90">
+    <row r="25" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" ht="90">
-      <c r="B26" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" ht="90">
-      <c r="B27" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" ht="90">
-      <c r="B28" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" ht="90">
-      <c r="B29" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E29" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>27</v>
@@ -8995,44 +8607,44 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="90">
+    <row r="30" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" ht="90">
-      <c r="B31" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="E31" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>18</v>
@@ -9047,16 +8659,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:14" ht="72">
+    <row r="32" spans="2:14" ht="66" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>18</v>
@@ -9065,56 +8677,56 @@
         <v>19</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M32" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="2:14" ht="90">
+    <row r="33" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="M33" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" ht="90">
-      <c r="B34" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E34" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>18</v>
@@ -9130,18 +8742,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="2:14" ht="90">
+    <row r="35" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>27</v>
@@ -9157,122 +8769,122 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:14" ht="90">
+    <row r="36" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14" ht="90">
-      <c r="B37" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M37" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="2:14" ht="90">
-      <c r="B38" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M38" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" ht="90">
-      <c r="B39" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="2:14" ht="90">
-      <c r="B40" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E40" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>27</v>
@@ -9288,18 +8900,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="2:14" ht="90">
+    <row r="41" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>27</v>
@@ -9314,21 +8926,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="2:14" ht="90">
+    <row r="42" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>39</v>
@@ -9343,18 +8955,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:14" ht="90">
+    <row r="43" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>18</v>
@@ -9369,16 +8981,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="2:14" ht="72">
+    <row r="44" spans="2:14" ht="66" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>18</v>
@@ -9387,27 +8999,27 @@
         <v>19</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="M44" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="90">
+    <row r="45" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>18</v>
@@ -9422,18 +9034,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:14" ht="90">
+    <row r="46" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>27</v>
@@ -9448,18 +9060,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="2:14" ht="90">
+    <row r="47" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>18</v>
@@ -9468,27 +9080,27 @@
         <v>19</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="M47" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="2:14" ht="90">
+    <row r="48" spans="2:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>18</v>
@@ -9497,27 +9109,27 @@
         <v>19</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="M48" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="2:13" ht="90">
+    <row r="49" spans="2:13" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>18</v>
@@ -9526,24 +9138,24 @@
         <v>19</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="M49" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="2:13" ht="90">
+    <row r="50" spans="2:13" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>18</v>
@@ -9552,24 +9164,24 @@
         <v>19</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="M50" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="2:13" ht="90">
+    <row r="51" spans="2:13" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>18</v>
@@ -9578,24 +9190,24 @@
         <v>19</v>
       </c>
       <c r="J51" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B52" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="M51" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="2:13" s="2" customFormat="1" ht="90">
-      <c r="B52" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>378</v>
-      </c>
       <c r="E52" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>18</v>
@@ -9604,24 +9216,24 @@
         <v>19</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="M52" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="2:13" s="2" customFormat="1" ht="90">
+    <row r="53" spans="2:13" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>18</v>
@@ -9630,24 +9242,24 @@
         <v>19</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="M53" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="2:13" s="2" customFormat="1" ht="90">
+    <row r="54" spans="2:13" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>18</v>
@@ -9656,24 +9268,24 @@
         <v>19</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M54" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="2:13" s="2" customFormat="1" ht="90">
+    <row r="55" spans="2:13" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>18</v>
@@ -9682,24 +9294,24 @@
         <v>19</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="M55" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="2:13" s="2" customFormat="1" ht="90">
+    <row r="56" spans="2:13" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>18</v>
@@ -9708,50 +9320,50 @@
         <v>19</v>
       </c>
       <c r="J56" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B57" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B58" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="M56" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="2:13" s="2" customFormat="1" ht="90">
-      <c r="B57" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13" s="2" customFormat="1" ht="90">
-      <c r="B58" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>393</v>
-      </c>
       <c r="E58" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>27</v>
@@ -9767,7 +9379,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="E2:E58">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"P5"</formula>
